--- a/data/output/sim_gridrnd/REL1/group_480_60/results/REL1_G3_results_summary.xlsx
+++ b/data/output/sim_gridrnd/REL1/group_480_60/results/REL1_G3_results_summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>mu</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jnd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>jnd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_trials</t>
@@ -466,1106 +466,1260 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>lat_entropy_100</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_120</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_140</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_180</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_200</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_40</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_60</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_80</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pse_40</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>jnd_40</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pse_60</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>jnd_60</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pse_80</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>jnd_80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pse_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>jnd_100</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pse_120</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>jnd_120</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pse_140</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jnd_140</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pse_160</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jnd_160</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pse_180</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>jnd_180</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pse_200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>jnd_200</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_40</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_60</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_80</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_100</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_120</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_140</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_160</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_180</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_200</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_40</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_60</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_80</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_100</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_120</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_140</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_160</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_180</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_200</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_40</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_60</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_80</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_100</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_120</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_140</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_160</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_180</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_200</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_40</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_60</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_80</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_100</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_120</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_140</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_160</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_180</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_200</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_40</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_60</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_80</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_100</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_120</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_140</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_160</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_180</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_200</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_40</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_60</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_80</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_100</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_120</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_140</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_160</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_180</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_200</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>pse_est</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>jnd_est</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S02_G3_478_58_REL1</t>
+          <t>S01_G3_479_59_REL1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C2" t="n">
-        <v>58</v>
+        <v>87.47220163083766</v>
       </c>
       <c r="D2" t="n">
-        <v>85.9896219421794</v>
+        <v>59</v>
       </c>
       <c r="E2" t="n">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F2" t="n">
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>473.8995237070131</v>
-      </c>
-      <c r="J2" t="n">
-        <v>79.16883533778223</v>
-      </c>
-      <c r="K2" t="n">
-        <v>457.7391178542318</v>
-      </c>
-      <c r="L2" t="n">
-        <v>110.7089313691188</v>
-      </c>
-      <c r="M2" t="n">
-        <v>478.1697033921321</v>
-      </c>
-      <c r="N2" t="n">
-        <v>100.4100988223498</v>
-      </c>
-      <c r="O2" t="n">
-        <v>479.2426739042192</v>
-      </c>
-      <c r="P2" t="n">
-        <v>94.46759574166688</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>479.0531044545106</v>
-      </c>
       <c r="R2" t="n">
-        <v>86.59715043464637</v>
+        <v>517.54</v>
       </c>
       <c r="S2" t="n">
-        <v>474.01073003</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>84.49380182044946</v>
+        <v>497.5</v>
       </c>
       <c r="U2" t="n">
-        <v>470.8679492670387</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>81.72177386095572</v>
+        <v>501.53</v>
       </c>
       <c r="W2" t="n">
-        <v>476.3702379262322</v>
+        <v>79.92</v>
       </c>
       <c r="X2" t="n">
-        <v>78.47176226962453</v>
+        <v>497.62</v>
       </c>
       <c r="Y2" t="n">
-        <v>483.3986162999846</v>
+        <v>74.77</v>
       </c>
       <c r="Z2" t="n">
-        <v>78.92373002008935</v>
+        <v>497.72</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>69.45</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>491.34</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>77.08</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>489.64</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>84.70999999999999</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>490.79</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>80.69</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>492.81</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>78.33</v>
       </c>
       <c r="AJ2" t="n">
-        <v>497.075</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>498.0666666666667</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>497.0375</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>497.85</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>497.8083333333333</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>498.5357142857143</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>497.3625</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>496.5722222222222</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>495.86</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>101.0676475188772</v>
+        <v>495.325</v>
       </c>
       <c r="AT2" t="n">
-        <v>105.7747396855958</v>
+        <v>496.7166666666666</v>
       </c>
       <c r="AU2" t="n">
-        <v>111.8083677268835</v>
+        <v>496.0125</v>
       </c>
       <c r="AV2" t="n">
-        <v>107.7941904742551</v>
+        <v>496.78</v>
       </c>
       <c r="AW2" t="n">
-        <v>107.3800335128567</v>
+        <v>496.625</v>
       </c>
       <c r="AX2" t="n">
-        <v>104.5250079929122</v>
+        <v>498.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>103.1680962979835</v>
+        <v>496.2625</v>
       </c>
       <c r="AZ2" t="n">
-        <v>99.62557851807803</v>
+        <v>496.6388888888889</v>
       </c>
       <c r="BA2" t="n">
-        <v>99.45225185987495</v>
+        <v>496.135</v>
       </c>
       <c r="BB2" t="n">
-        <v>352</v>
+        <v>96.72315842134189</v>
       </c>
       <c r="BC2" t="n">
-        <v>345</v>
+        <v>89.49079872006706</v>
       </c>
       <c r="BD2" t="n">
-        <v>341</v>
+        <v>89.6739223171932</v>
       </c>
       <c r="BE2" t="n">
-        <v>341</v>
+        <v>82.33293144301373</v>
       </c>
       <c r="BF2" t="n">
-        <v>341</v>
+        <v>77.04220299074181</v>
       </c>
       <c r="BG2" t="n">
-        <v>341</v>
+        <v>85.57045551557417</v>
       </c>
       <c r="BH2" t="n">
-        <v>341</v>
+        <v>90.48338849617647</v>
       </c>
       <c r="BI2" t="n">
-        <v>341</v>
+        <v>92.78300633969616</v>
       </c>
       <c r="BJ2" t="n">
-        <v>341</v>
+        <v>91.7523665907316</v>
       </c>
       <c r="BK2" t="n">
-        <v>688</v>
+        <v>326</v>
       </c>
       <c r="BL2" t="n">
-        <v>688</v>
+        <v>326</v>
       </c>
       <c r="BM2" t="n">
-        <v>688</v>
+        <v>326</v>
       </c>
       <c r="BN2" t="n">
-        <v>688</v>
+        <v>326</v>
       </c>
       <c r="BO2" t="n">
-        <v>688</v>
+        <v>326</v>
       </c>
       <c r="BP2" t="n">
-        <v>688</v>
+        <v>326</v>
       </c>
       <c r="BQ2" t="n">
-        <v>688</v>
+        <v>326</v>
       </c>
       <c r="BR2" t="n">
-        <v>688</v>
+        <v>326</v>
       </c>
       <c r="BS2" t="n">
-        <v>688</v>
+        <v>326</v>
       </c>
       <c r="BT2" t="n">
+        <v>639</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>639</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>639</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>639</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>639</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>642</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>642</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>645</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>645</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="CJ2" t="n">
         <v>1</v>
       </c>
-      <c r="BU2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>0.9</v>
+      <c r="CK2" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>492.81</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>78.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S03_G3_481_60_REL1</t>
+          <t>S02_G3_478_58_REL1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C3" t="n">
-        <v>60</v>
+        <v>85.9896219421794</v>
       </c>
       <c r="D3" t="n">
-        <v>88.95478131949592</v>
+        <v>58</v>
       </c>
       <c r="E3" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F3" t="n">
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>466.6989832211754</v>
-      </c>
-      <c r="J3" t="n">
-        <v>68.8773729393029</v>
-      </c>
-      <c r="K3" t="n">
-        <v>479.4505022606469</v>
-      </c>
-      <c r="L3" t="n">
-        <v>57.01274586142447</v>
-      </c>
-      <c r="M3" t="n">
-        <v>480.3552934997593</v>
-      </c>
-      <c r="N3" t="n">
-        <v>52.68742371814752</v>
-      </c>
-      <c r="O3" t="n">
-        <v>482.2166073930575</v>
-      </c>
-      <c r="P3" t="n">
-        <v>50.62623957342233</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>484.2487784876444</v>
-      </c>
       <c r="R3" t="n">
-        <v>52.09132061612895</v>
+        <v>473.9</v>
       </c>
       <c r="S3" t="n">
-        <v>488.9388763451701</v>
+        <v>79.17</v>
       </c>
       <c r="T3" t="n">
-        <v>49.9850648354509</v>
+        <v>457.74</v>
       </c>
       <c r="U3" t="n">
-        <v>486.6061224165424</v>
+        <v>110.71</v>
       </c>
       <c r="V3" t="n">
-        <v>52.59251501352598</v>
+        <v>478.17</v>
       </c>
       <c r="W3" t="n">
-        <v>484.0226294169501</v>
+        <v>100.41</v>
       </c>
       <c r="X3" t="n">
-        <v>63.15931452444562</v>
+        <v>479.24</v>
       </c>
       <c r="Y3" t="n">
-        <v>482.8022645125691</v>
+        <v>94.47</v>
       </c>
       <c r="Z3" t="n">
-        <v>67.53308231947904</v>
+        <v>479.05</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>474.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>470.87</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>81.72</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>476.37</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>78.47</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>483.4</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>78.92</v>
       </c>
       <c r="AJ3" t="n">
-        <v>495.475</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>497.2666666666667</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>496.9</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>496.83</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>498.2833333333334</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>498.6142857142857</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>500.0125</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>500.3833333333333</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>500.445</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>88.22527628180033</v>
+        <v>497.075</v>
       </c>
       <c r="AT3" t="n">
-        <v>81.35393181784283</v>
+        <v>498.0666666666667</v>
       </c>
       <c r="AU3" t="n">
-        <v>76.29590421510188</v>
+        <v>497.0375</v>
       </c>
       <c r="AV3" t="n">
-        <v>71.6894769125846</v>
+        <v>497.85</v>
       </c>
       <c r="AW3" t="n">
-        <v>69.82599603458745</v>
+        <v>497.8083333333333</v>
       </c>
       <c r="AX3" t="n">
-        <v>68.07155748751097</v>
+        <v>498.5357142857143</v>
       </c>
       <c r="AY3" t="n">
-        <v>69.48497926710492</v>
+        <v>497.3625</v>
       </c>
       <c r="AZ3" t="n">
-        <v>73.5475110992132</v>
+        <v>496.5722222222222</v>
       </c>
       <c r="BA3" t="n">
-        <v>80.54630329816509</v>
+        <v>495.86</v>
       </c>
       <c r="BB3" t="n">
+        <v>101.0676475188772</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>105.7747396855958</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>111.8083677268835</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>107.7941904742551</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>107.3800335128567</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>104.5250079929122</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>103.1680962979835</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>99.62557851807803</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>99.45225185987495</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>352</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>345</v>
+      </c>
+      <c r="BM3" t="n">
         <v>341</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BN3" t="n">
         <v>341</v>
       </c>
-      <c r="BD3" t="n">
+      <c r="BO3" t="n">
         <v>341</v>
       </c>
-      <c r="BE3" t="n">
+      <c r="BP3" t="n">
         <v>341</v>
       </c>
-      <c r="BF3" t="n">
+      <c r="BQ3" t="n">
         <v>341</v>
       </c>
-      <c r="BG3" t="n">
+      <c r="BR3" t="n">
         <v>341</v>
       </c>
-      <c r="BH3" t="n">
+      <c r="BS3" t="n">
         <v>341</v>
       </c>
-      <c r="BI3" t="n">
-        <v>341</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>341</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>669</v>
-      </c>
       <c r="BT3" t="n">
-        <v>0.8333333333333334</v>
+        <v>688</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.2222222222222222</v>
+        <v>688</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.9166666666666666</v>
+        <v>688</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.9166666666666666</v>
+        <v>688</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.9230769230769231</v>
+        <v>688</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.9333333333333333</v>
+        <v>688</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.8947368421052632</v>
+        <v>688</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.8181818181818182</v>
+        <v>688</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.8181818181818182</v>
+        <v>688</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>483.4</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>78.92</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S01_G3_479_59_REL1</t>
+          <t>S03_G3_481_60_REL1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C4" t="n">
-        <v>59</v>
+        <v>88.95478131949592</v>
       </c>
       <c r="D4" t="n">
-        <v>87.47220163083766</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="F4" t="n">
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>517.5402565251926</v>
-      </c>
-      <c r="J4" t="n">
-        <v>68.43364784500142</v>
-      </c>
-      <c r="K4" t="n">
-        <v>497.5043286076383</v>
-      </c>
-      <c r="L4" t="n">
-        <v>86.31503388975385</v>
-      </c>
-      <c r="M4" t="n">
-        <v>501.5273113552455</v>
-      </c>
-      <c r="N4" t="n">
-        <v>79.9178581153185</v>
-      </c>
-      <c r="O4" t="n">
-        <v>497.6213322122471</v>
-      </c>
-      <c r="P4" t="n">
-        <v>74.77279201252959</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>497.71605555941</v>
-      </c>
       <c r="R4" t="n">
-        <v>69.45253049044666</v>
+        <v>466.7</v>
       </c>
       <c r="S4" t="n">
-        <v>491.3392669717455</v>
+        <v>68.88</v>
       </c>
       <c r="T4" t="n">
-        <v>77.08379251101616</v>
+        <v>479.45</v>
       </c>
       <c r="U4" t="n">
-        <v>489.6412085104482</v>
+        <v>57.01</v>
       </c>
       <c r="V4" t="n">
-        <v>84.7134351369557</v>
+        <v>480.36</v>
       </c>
       <c r="W4" t="n">
-        <v>490.7918800151336</v>
+        <v>52.69</v>
       </c>
       <c r="X4" t="n">
-        <v>80.69029304140874</v>
+        <v>482.22</v>
       </c>
       <c r="Y4" t="n">
-        <v>492.8132280721579</v>
+        <v>50.63</v>
       </c>
       <c r="Z4" t="n">
-        <v>78.33319057727596</v>
+        <v>484.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>52.09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>488.94</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>49.99</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>486.61</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>52.59</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>484.02</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>63.16</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>482.8</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>67.53</v>
       </c>
       <c r="AJ4" t="n">
-        <v>495.325</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>496.7166666666666</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>496.0125</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>496.78</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>496.625</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>498.2</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>496.2625</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>496.6388888888889</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>496.135</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>96.72315842134189</v>
+        <v>495.475</v>
       </c>
       <c r="AT4" t="n">
-        <v>89.49079872006706</v>
+        <v>497.2666666666667</v>
       </c>
       <c r="AU4" t="n">
-        <v>89.6739223171932</v>
+        <v>496.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>82.33293144301373</v>
+        <v>496.83</v>
       </c>
       <c r="AW4" t="n">
-        <v>77.04220299074181</v>
+        <v>498.2833333333334</v>
       </c>
       <c r="AX4" t="n">
-        <v>85.57045551557417</v>
+        <v>498.6142857142857</v>
       </c>
       <c r="AY4" t="n">
-        <v>90.48338849617647</v>
+        <v>500.0125</v>
       </c>
       <c r="AZ4" t="n">
-        <v>92.78300633969616</v>
+        <v>500.3833333333333</v>
       </c>
       <c r="BA4" t="n">
-        <v>91.7523665907316</v>
+        <v>500.445</v>
       </c>
       <c r="BB4" t="n">
-        <v>326</v>
+        <v>88.22527628180033</v>
       </c>
       <c r="BC4" t="n">
-        <v>326</v>
+        <v>81.35393181784283</v>
       </c>
       <c r="BD4" t="n">
-        <v>326</v>
+        <v>76.29590421510188</v>
       </c>
       <c r="BE4" t="n">
-        <v>326</v>
+        <v>71.6894769125846</v>
       </c>
       <c r="BF4" t="n">
-        <v>326</v>
+        <v>69.82599603458745</v>
       </c>
       <c r="BG4" t="n">
-        <v>326</v>
+        <v>68.07155748751097</v>
       </c>
       <c r="BH4" t="n">
-        <v>326</v>
+        <v>69.48497926710492</v>
       </c>
       <c r="BI4" t="n">
-        <v>326</v>
+        <v>73.5475110992132</v>
       </c>
       <c r="BJ4" t="n">
-        <v>326</v>
+        <v>80.54630329816509</v>
       </c>
       <c r="BK4" t="n">
-        <v>639</v>
+        <v>341</v>
       </c>
       <c r="BL4" t="n">
-        <v>639</v>
+        <v>341</v>
       </c>
       <c r="BM4" t="n">
-        <v>639</v>
+        <v>341</v>
       </c>
       <c r="BN4" t="n">
-        <v>639</v>
+        <v>341</v>
       </c>
       <c r="BO4" t="n">
-        <v>639</v>
+        <v>341</v>
       </c>
       <c r="BP4" t="n">
-        <v>642</v>
+        <v>341</v>
       </c>
       <c r="BQ4" t="n">
-        <v>642</v>
+        <v>341</v>
       </c>
       <c r="BR4" t="n">
-        <v>645</v>
+        <v>341</v>
       </c>
       <c r="BS4" t="n">
-        <v>645</v>
+        <v>341</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.4615384615384616</v>
+        <v>669</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.6666666666666666</v>
+        <v>669</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.6666666666666666</v>
+        <v>669</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.8</v>
+        <v>669</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.7857142857142857</v>
+        <v>669</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.7857142857142857</v>
+        <v>669</v>
       </c>
       <c r="CA4" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.8421052631578947</v>
+        <v>669</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>482.8</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>67.53</v>
       </c>
     </row>
     <row r="5">
@@ -1578,10 +1732,10 @@
         <v>481</v>
       </c>
       <c r="C5" t="n">
+        <v>90.43736100815418</v>
+      </c>
+      <c r="D5" t="n">
         <v>61</v>
-      </c>
-      <c r="D5" t="n">
-        <v>90.43736100815418</v>
       </c>
       <c r="E5" t="n">
         <v>481</v>
@@ -1590,720 +1744,819 @@
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>491.9797578837207</v>
-      </c>
-      <c r="J5" t="n">
-        <v>54.99401428710365</v>
-      </c>
-      <c r="K5" t="n">
-        <v>494.81815094302</v>
-      </c>
-      <c r="L5" t="n">
-        <v>54.54492861262047</v>
-      </c>
-      <c r="M5" t="n">
-        <v>486.8380254718712</v>
-      </c>
-      <c r="N5" t="n">
-        <v>54.55683486579799</v>
-      </c>
-      <c r="O5" t="n">
-        <v>483.9081185008652</v>
-      </c>
-      <c r="P5" t="n">
-        <v>54.2296898422567</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>478.6587185925393</v>
-      </c>
       <c r="R5" t="n">
-        <v>54.73530686523389</v>
+        <v>491.98</v>
       </c>
       <c r="S5" t="n">
-        <v>480.9895315973912</v>
+        <v>54.99</v>
       </c>
       <c r="T5" t="n">
-        <v>59.79533362414298</v>
+        <v>494.82</v>
       </c>
       <c r="U5" t="n">
-        <v>483.6074727784815</v>
+        <v>54.54</v>
       </c>
       <c r="V5" t="n">
-        <v>57.16509572278406</v>
+        <v>486.84</v>
       </c>
       <c r="W5" t="n">
-        <v>482.1461241548723</v>
+        <v>54.56</v>
       </c>
       <c r="X5" t="n">
-        <v>57.74391456233046</v>
+        <v>483.91</v>
       </c>
       <c r="Y5" t="n">
-        <v>485.7347321823509</v>
+        <v>54.23</v>
       </c>
       <c r="Z5" t="n">
-        <v>59.62811670770751</v>
+        <v>478.66</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>54.74</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>480.99</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>59.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>483.61</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>57.17</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>482.15</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>57.74</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>485.73</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>59.63</v>
       </c>
       <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
         <v>499.925</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AT5" t="n">
         <v>499.9333333333333</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AU5" t="n">
         <v>500.0625</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AV5" t="n">
         <v>499.79</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AW5" t="n">
         <v>500.0333333333334</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AX5" t="n">
         <v>500.0142857142857</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AY5" t="n">
         <v>500.46875</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AZ5" t="n">
         <v>500.3166666666667</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="BA5" t="n">
         <v>499.7</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="BB5" t="n">
         <v>65.43637654240949</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="BC5" t="n">
         <v>62.57791587737287</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="BD5" t="n">
         <v>60.49883134201851</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="BE5" t="n">
         <v>61.16000245258334</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="BF5" t="n">
         <v>59.34699280970819</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="BG5" t="n">
         <v>60.27081569457805</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="BH5" t="n">
         <v>61.7678032913386</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BI5" t="n">
         <v>62.60231403248783</v>
       </c>
-      <c r="BA5" t="n">
+      <c r="BJ5" t="n">
         <v>64.22390520670632</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BK5" t="n">
         <v>363</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BL5" t="n">
         <v>363</v>
       </c>
-      <c r="BD5" t="n">
+      <c r="BM5" t="n">
         <v>363</v>
       </c>
-      <c r="BE5" t="n">
+      <c r="BN5" t="n">
         <v>363</v>
       </c>
-      <c r="BF5" t="n">
+      <c r="BO5" t="n">
         <v>363</v>
       </c>
-      <c r="BG5" t="n">
+      <c r="BP5" t="n">
         <v>363</v>
       </c>
-      <c r="BH5" t="n">
+      <c r="BQ5" t="n">
         <v>363</v>
       </c>
-      <c r="BI5" t="n">
+      <c r="BR5" t="n">
         <v>363</v>
       </c>
-      <c r="BJ5" t="n">
+      <c r="BS5" t="n">
         <v>363</v>
       </c>
-      <c r="BK5" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>669</v>
-      </c>
       <c r="BT5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC5" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="BU5" t="n">
+      <c r="CD5" t="n">
         <v>1</v>
       </c>
-      <c r="BV5" t="n">
+      <c r="CE5" t="n">
         <v>0.8620689655172413</v>
       </c>
-      <c r="BW5" t="n">
+      <c r="CF5" t="n">
         <v>0.90625</v>
       </c>
-      <c r="BX5" t="n">
+      <c r="CG5" t="n">
         <v>0.8947368421052632</v>
       </c>
-      <c r="BY5" t="n">
+      <c r="CH5" t="n">
         <v>0.925</v>
       </c>
-      <c r="BZ5" t="n">
+      <c r="CI5" t="n">
         <v>0.975</v>
       </c>
-      <c r="CA5" t="n">
+      <c r="CJ5" t="n">
         <v>1</v>
       </c>
-      <c r="CB5" t="n">
+      <c r="CK5" t="n">
         <v>1</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>485.73</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>59.63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S06_G3_481_61_REL1</t>
+          <t>S05_G3_478_58_REL1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C6" t="n">
-        <v>61</v>
+        <v>85.9896219421794</v>
       </c>
       <c r="D6" t="n">
-        <v>90.43736100815418</v>
+        <v>58</v>
       </c>
       <c r="E6" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F6" t="n">
         <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>482.9453853752353</v>
-      </c>
-      <c r="J6" t="n">
-        <v>54.31176109897489</v>
-      </c>
-      <c r="K6" t="n">
-        <v>495.1453681634327</v>
-      </c>
-      <c r="L6" t="n">
-        <v>52.5668606968881</v>
-      </c>
-      <c r="M6" t="n">
-        <v>494.0606629292068</v>
-      </c>
-      <c r="N6" t="n">
-        <v>48.35932826419874</v>
-      </c>
-      <c r="O6" t="n">
-        <v>483.5490131394627</v>
-      </c>
-      <c r="P6" t="n">
-        <v>50.82040601550823</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>481.9567871373973</v>
-      </c>
       <c r="R6" t="n">
-        <v>56.30596300785069</v>
+        <v>441.44</v>
       </c>
       <c r="S6" t="n">
-        <v>483.3954346999006</v>
+        <v>22.17</v>
       </c>
       <c r="T6" t="n">
-        <v>52.85002095110069</v>
+        <v>440.27</v>
       </c>
       <c r="U6" t="n">
-        <v>486.1257383832582</v>
+        <v>52.27</v>
       </c>
       <c r="V6" t="n">
-        <v>55.77189649139654</v>
+        <v>462.43</v>
       </c>
       <c r="W6" t="n">
-        <v>486.6404506806352</v>
+        <v>72.95999999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>54.44906122461671</v>
+        <v>462.44</v>
       </c>
       <c r="Y6" t="n">
-        <v>483.7721120648625</v>
+        <v>69.68000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>58.18201440793552</v>
+        <v>463.76</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>62.57</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>459.81</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>60.64</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>457.85</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>55.88</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>459.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>59.18</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>462.83</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>66.25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>501.25</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>500.75</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>501.125</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>501.5</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>501.875</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>502.1428571428572</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>502.43125</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>502.5166666666667</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>502.485</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>83.01980185473825</v>
+        <v>498.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>76.33863700643337</v>
+        <v>497.7</v>
       </c>
       <c r="AU6" t="n">
-        <v>70.06485834567854</v>
+        <v>495.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>64.55315639068317</v>
+        <v>496.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>65.78330113587592</v>
+        <v>496.2333333333333</v>
       </c>
       <c r="AX6" t="n">
-        <v>66.21497148666298</v>
+        <v>496.65</v>
       </c>
       <c r="AY6" t="n">
-        <v>64.87204924647826</v>
+        <v>497.28125</v>
       </c>
       <c r="AZ6" t="n">
-        <v>65.05950054458695</v>
+        <v>498.0111111111111</v>
       </c>
       <c r="BA6" t="n">
-        <v>65.2629280296249</v>
+        <v>496.875</v>
       </c>
       <c r="BB6" t="n">
-        <v>356</v>
+        <v>76.29947575180316</v>
       </c>
       <c r="BC6" t="n">
-        <v>356</v>
+        <v>85.38096977664286</v>
       </c>
       <c r="BD6" t="n">
-        <v>356</v>
+        <v>91.25204107306314</v>
       </c>
       <c r="BE6" t="n">
-        <v>356</v>
+        <v>90.73488854900302</v>
       </c>
       <c r="BF6" t="n">
-        <v>356</v>
+        <v>87.21742308099276</v>
       </c>
       <c r="BG6" t="n">
-        <v>356</v>
+        <v>81.82393336566368</v>
       </c>
       <c r="BH6" t="n">
-        <v>356</v>
+        <v>80.82513314828192</v>
       </c>
       <c r="BI6" t="n">
-        <v>356</v>
+        <v>80.20972432656286</v>
       </c>
       <c r="BJ6" t="n">
-        <v>356</v>
+        <v>80.58423775776501</v>
       </c>
       <c r="BK6" t="n">
-        <v>669</v>
+        <v>339</v>
       </c>
       <c r="BL6" t="n">
-        <v>669</v>
+        <v>339</v>
       </c>
       <c r="BM6" t="n">
-        <v>669</v>
+        <v>339</v>
       </c>
       <c r="BN6" t="n">
-        <v>669</v>
+        <v>339</v>
       </c>
       <c r="BO6" t="n">
-        <v>669</v>
+        <v>339</v>
       </c>
       <c r="BP6" t="n">
-        <v>669</v>
+        <v>339</v>
       </c>
       <c r="BQ6" t="n">
-        <v>669</v>
+        <v>339</v>
       </c>
       <c r="BR6" t="n">
-        <v>669</v>
+        <v>339</v>
       </c>
       <c r="BS6" t="n">
-        <v>669</v>
+        <v>339</v>
       </c>
       <c r="BT6" t="n">
+        <v>609</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>618</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>630</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>630</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>630</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>630</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>630</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>630</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>630</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="CD6" t="n">
         <v>0.8</v>
       </c>
-      <c r="BU6" t="n">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>0.07142857142857142</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>0.06666666666666667</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="BY6" t="n">
+      <c r="CE6" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="CH6" t="n">
         <v>0.8823529411764706</v>
       </c>
-      <c r="BZ6" t="n">
-        <v>0.9523809523809523</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>0.7931034482758621</v>
+      <c r="CI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>462.83</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>66.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S05_G3_478_58_REL1</t>
+          <t>S06_G3_481_61_REL1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C7" t="n">
-        <v>58</v>
+        <v>90.43736100815418</v>
       </c>
       <c r="D7" t="n">
-        <v>85.9896219421794</v>
+        <v>61</v>
       </c>
       <c r="E7" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F7" t="n">
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>441.4433442766717</v>
-      </c>
-      <c r="J7" t="n">
-        <v>22.17188641173982</v>
-      </c>
-      <c r="K7" t="n">
-        <v>440.2662296104797</v>
-      </c>
-      <c r="L7" t="n">
-        <v>52.26879466278693</v>
-      </c>
-      <c r="M7" t="n">
-        <v>462.4296675231454</v>
-      </c>
-      <c r="N7" t="n">
-        <v>72.9629593368774</v>
-      </c>
-      <c r="O7" t="n">
-        <v>462.4376736648979</v>
-      </c>
-      <c r="P7" t="n">
-        <v>69.67577014115771</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>463.7558491117679</v>
-      </c>
       <c r="R7" t="n">
-        <v>62.56640590725568</v>
+        <v>482.95</v>
       </c>
       <c r="S7" t="n">
-        <v>459.8072496449199</v>
+        <v>54.31</v>
       </c>
       <c r="T7" t="n">
-        <v>60.64436294434032</v>
+        <v>495.15</v>
       </c>
       <c r="U7" t="n">
-        <v>457.8529618429457</v>
+        <v>52.57</v>
       </c>
       <c r="V7" t="n">
-        <v>55.8824994014608</v>
+        <v>494.06</v>
       </c>
       <c r="W7" t="n">
-        <v>459.5041957110412</v>
+        <v>48.36</v>
       </c>
       <c r="X7" t="n">
-        <v>59.17507980850991</v>
+        <v>483.55</v>
       </c>
       <c r="Y7" t="n">
-        <v>462.8326926149443</v>
+        <v>50.82</v>
       </c>
       <c r="Z7" t="n">
-        <v>66.25456302456809</v>
+        <v>481.96</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>56.31</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>483.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>52.85</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>486.13</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>55.77</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>486.64</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>54.45</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>483.77</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>58.18</v>
       </c>
       <c r="AJ7" t="n">
-        <v>498.2</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>497.7</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>495.2</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>496.2</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>496.2333333333333</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>496.65</v>
+        <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>497.28125</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>498.0111111111111</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>496.875</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>76.29947575180316</v>
+        <v>501.25</v>
       </c>
       <c r="AT7" t="n">
-        <v>85.38096977664286</v>
+        <v>500.75</v>
       </c>
       <c r="AU7" t="n">
-        <v>91.25204107306314</v>
+        <v>501.125</v>
       </c>
       <c r="AV7" t="n">
-        <v>90.73488854900302</v>
+        <v>501.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>87.21742308099276</v>
+        <v>501.875</v>
       </c>
       <c r="AX7" t="n">
-        <v>81.82393336566368</v>
+        <v>502.1428571428572</v>
       </c>
       <c r="AY7" t="n">
-        <v>80.82513314828192</v>
+        <v>502.43125</v>
       </c>
       <c r="AZ7" t="n">
-        <v>80.20972432656286</v>
+        <v>502.5166666666667</v>
       </c>
       <c r="BA7" t="n">
-        <v>80.58423775776501</v>
+        <v>502.485</v>
       </c>
       <c r="BB7" t="n">
-        <v>339</v>
+        <v>83.01980185473825</v>
       </c>
       <c r="BC7" t="n">
-        <v>339</v>
+        <v>76.33863700643337</v>
       </c>
       <c r="BD7" t="n">
-        <v>339</v>
+        <v>70.06485834567854</v>
       </c>
       <c r="BE7" t="n">
-        <v>339</v>
+        <v>64.55315639068317</v>
       </c>
       <c r="BF7" t="n">
-        <v>339</v>
+        <v>65.78330113587592</v>
       </c>
       <c r="BG7" t="n">
-        <v>339</v>
+        <v>66.21497148666298</v>
       </c>
       <c r="BH7" t="n">
-        <v>339</v>
+        <v>64.87204924647826</v>
       </c>
       <c r="BI7" t="n">
-        <v>339</v>
+        <v>65.05950054458695</v>
       </c>
       <c r="BJ7" t="n">
-        <v>339</v>
+        <v>65.2629280296249</v>
       </c>
       <c r="BK7" t="n">
-        <v>609</v>
+        <v>356</v>
       </c>
       <c r="BL7" t="n">
-        <v>618</v>
+        <v>356</v>
       </c>
       <c r="BM7" t="n">
-        <v>630</v>
+        <v>356</v>
       </c>
       <c r="BN7" t="n">
-        <v>630</v>
+        <v>356</v>
       </c>
       <c r="BO7" t="n">
-        <v>630</v>
+        <v>356</v>
       </c>
       <c r="BP7" t="n">
-        <v>630</v>
+        <v>356</v>
       </c>
       <c r="BQ7" t="n">
-        <v>630</v>
+        <v>356</v>
       </c>
       <c r="BR7" t="n">
-        <v>630</v>
+        <v>356</v>
       </c>
       <c r="BS7" t="n">
-        <v>630</v>
+        <v>356</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.6363636363636364</v>
+        <v>669</v>
       </c>
       <c r="BU7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC7" t="n">
         <v>0.8</v>
       </c>
-      <c r="BV7" t="n">
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="BY7" t="n">
+      <c r="CD7" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CH7" t="n">
         <v>0.8823529411764706</v>
       </c>
-      <c r="BZ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>0.9473684210526315</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>1</v>
+      <c r="CI7" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.7931034482758621</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>483.77</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>58.18</v>
       </c>
     </row>
     <row r="8">
@@ -2316,10 +2569,10 @@
         <v>479</v>
       </c>
       <c r="C8" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D8" t="n">
         <v>58</v>
-      </c>
-      <c r="D8" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E8" t="n">
         <v>479</v>
@@ -2328,228 +2581,261 @@
         <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>478.3943156841451</v>
-      </c>
-      <c r="J8" t="n">
-        <v>70.55046438612789</v>
-      </c>
-      <c r="K8" t="n">
-        <v>465.4633282200919</v>
-      </c>
-      <c r="L8" t="n">
-        <v>61.49904919241345</v>
-      </c>
-      <c r="M8" t="n">
-        <v>464.5702566220064</v>
-      </c>
-      <c r="N8" t="n">
-        <v>60.38166587347816</v>
-      </c>
-      <c r="O8" t="n">
-        <v>469.9172009142844</v>
-      </c>
-      <c r="P8" t="n">
-        <v>62.30713550693784</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>473.7932036649977</v>
-      </c>
       <c r="R8" t="n">
-        <v>57.64210820395576</v>
+        <v>478.39</v>
       </c>
       <c r="S8" t="n">
-        <v>468.4437797587309</v>
+        <v>70.55</v>
       </c>
       <c r="T8" t="n">
-        <v>57.41220765886686</v>
+        <v>465.46</v>
       </c>
       <c r="U8" t="n">
-        <v>473.2273427623915</v>
+        <v>61.5</v>
       </c>
       <c r="V8" t="n">
-        <v>57.92711365886673</v>
+        <v>464.57</v>
       </c>
       <c r="W8" t="n">
-        <v>470.4731588616898</v>
+        <v>60.38</v>
       </c>
       <c r="X8" t="n">
-        <v>58.57917844218657</v>
+        <v>469.92</v>
       </c>
       <c r="Y8" t="n">
-        <v>470.8934023932767</v>
+        <v>62.31</v>
       </c>
       <c r="Z8" t="n">
-        <v>57.36828704893126</v>
+        <v>473.79</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>57.64</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>468.44</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>57.41</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>473.23</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>57.93</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>470.47</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>58.58</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>470.89</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>57.37</v>
       </c>
       <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
         <v>501.7</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AT8" t="n">
         <v>500.5166666666667</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AU8" t="n">
         <v>501.3125</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AV8" t="n">
         <v>500.95</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AW8" t="n">
         <v>500.45</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AX8" t="n">
         <v>499.2428571428571</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AY8" t="n">
         <v>499.825</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AZ8" t="n">
         <v>498.8944444444444</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="BA8" t="n">
         <v>497.895</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="BB8" t="n">
         <v>108.262689787387</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="BC8" t="n">
         <v>98.02338014757274</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="BD8" t="n">
         <v>90.08920492350902</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="BE8" t="n">
         <v>84.993573286455</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="BF8" t="n">
         <v>79.9988385332354</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="BG8" t="n">
         <v>77.43816624789571</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="BH8" t="n">
         <v>76.40398795220051</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BI8" t="n">
         <v>75.56781334391148</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BJ8" t="n">
         <v>72.74189972086239</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BK8" t="n">
         <v>327</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BL8" t="n">
         <v>327</v>
       </c>
-      <c r="BD8" t="n">
+      <c r="BM8" t="n">
         <v>327</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="BN8" t="n">
         <v>327</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="BO8" t="n">
         <v>327</v>
       </c>
-      <c r="BG8" t="n">
+      <c r="BP8" t="n">
         <v>327</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BQ8" t="n">
         <v>327</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BR8" t="n">
         <v>327</v>
       </c>
-      <c r="BJ8" t="n">
+      <c r="BS8" t="n">
         <v>327</v>
       </c>
-      <c r="BK8" t="n">
+      <c r="BT8" t="n">
         <v>652</v>
       </c>
-      <c r="BL8" t="n">
+      <c r="BU8" t="n">
         <v>652</v>
       </c>
-      <c r="BM8" t="n">
+      <c r="BV8" t="n">
         <v>652</v>
       </c>
-      <c r="BN8" t="n">
+      <c r="BW8" t="n">
         <v>652</v>
       </c>
-      <c r="BO8" t="n">
+      <c r="BX8" t="n">
         <v>652</v>
       </c>
-      <c r="BP8" t="n">
+      <c r="BY8" t="n">
         <v>652</v>
       </c>
-      <c r="BQ8" t="n">
+      <c r="BZ8" t="n">
         <v>652</v>
       </c>
-      <c r="BR8" t="n">
+      <c r="CA8" t="n">
         <v>652</v>
       </c>
-      <c r="BS8" t="n">
+      <c r="CB8" t="n">
         <v>652</v>
       </c>
-      <c r="BT8" t="n">
+      <c r="CC8" t="n">
         <v>0.875</v>
       </c>
-      <c r="BU8" t="n">
+      <c r="CD8" t="n">
         <v>1</v>
       </c>
-      <c r="BV8" t="n">
+      <c r="CE8" t="n">
         <v>0.5882352941176471</v>
       </c>
-      <c r="BW8" t="n">
+      <c r="CF8" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="BX8" t="n">
+      <c r="CG8" t="n">
         <v>0.6538461538461539</v>
       </c>
-      <c r="BY8" t="n">
+      <c r="CH8" t="n">
         <v>0.8076923076923077</v>
       </c>
-      <c r="BZ8" t="n">
+      <c r="CI8" t="n">
         <v>0.8846153846153846</v>
       </c>
-      <c r="CA8" t="n">
+      <c r="CJ8" t="n">
         <v>0.8846153846153846</v>
       </c>
-      <c r="CB8" t="n">
+      <c r="CK8" t="n">
         <v>0.8846153846153846</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>470.89</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>57.37</v>
       </c>
     </row>
     <row r="9">
@@ -2562,10 +2848,10 @@
         <v>478</v>
       </c>
       <c r="C9" t="n">
+        <v>87.47220163083766</v>
+      </c>
+      <c r="D9" t="n">
         <v>59</v>
-      </c>
-      <c r="D9" t="n">
-        <v>87.47220163083766</v>
       </c>
       <c r="E9" t="n">
         <v>478</v>
@@ -2574,228 +2860,261 @@
         <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>76</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>487.1375493631132</v>
-      </c>
-      <c r="J9" t="n">
-        <v>46.78464013176908</v>
-      </c>
-      <c r="K9" t="n">
-        <v>470.9025110822325</v>
-      </c>
-      <c r="L9" t="n">
-        <v>61.79809830208276</v>
-      </c>
-      <c r="M9" t="n">
-        <v>462.8414014504269</v>
-      </c>
-      <c r="N9" t="n">
-        <v>57.22187353306873</v>
-      </c>
-      <c r="O9" t="n">
-        <v>468.0304454974797</v>
-      </c>
-      <c r="P9" t="n">
-        <v>64.86291401839669</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>468.4759787630022</v>
-      </c>
       <c r="R9" t="n">
-        <v>61.74144771576562</v>
+        <v>487.14</v>
       </c>
       <c r="S9" t="n">
-        <v>473.391960031531</v>
+        <v>46.78</v>
       </c>
       <c r="T9" t="n">
-        <v>66.77382117839971</v>
+        <v>470.9</v>
       </c>
       <c r="U9" t="n">
-        <v>471.7307272485149</v>
+        <v>61.8</v>
       </c>
       <c r="V9" t="n">
-        <v>72.22392598779098</v>
+        <v>462.84</v>
       </c>
       <c r="W9" t="n">
-        <v>470.2304290973338</v>
+        <v>57.22</v>
       </c>
       <c r="X9" t="n">
-        <v>67.36187231375054</v>
+        <v>468.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>470.6964791222236</v>
+        <v>64.86</v>
       </c>
       <c r="Z9" t="n">
-        <v>69.61482462714983</v>
+        <v>468.48</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>61.74</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>473.39</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>66.77</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>471.73</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>72.22</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>470.23</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>67.36</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>470.7</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>69.61</v>
       </c>
       <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
         <v>504.3</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AT9" t="n">
         <v>502.5833333333333</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AU9" t="n">
         <v>503.7</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AV9" t="n">
         <v>498.69</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AW9" t="n">
         <v>500.8416666666666</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AX9" t="n">
         <v>501.1642857142857</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AY9" t="n">
         <v>500.6875</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AZ9" t="n">
         <v>500.9055555555556</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="BA9" t="n">
         <v>500.575</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="BB9" t="n">
         <v>76.94842428536143</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="BC9" t="n">
         <v>77.65549812401494</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="BD9" t="n">
         <v>81.09784214145282</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="BE9" t="n">
         <v>84.35860299933847</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="BF9" t="n">
         <v>82.95289786311801</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="BG9" t="n">
         <v>81.65813848988142</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="BH9" t="n">
         <v>80.45217426365804</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BI9" t="n">
         <v>80.24086636996431</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BJ9" t="n">
         <v>81.12419105914093</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BK9" t="n">
         <v>367</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BL9" t="n">
         <v>367</v>
       </c>
-      <c r="BD9" t="n">
+      <c r="BM9" t="n">
         <v>367</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BN9" t="n">
         <v>367</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BO9" t="n">
         <v>367</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BP9" t="n">
         <v>367</v>
       </c>
-      <c r="BH9" t="n">
+      <c r="BQ9" t="n">
         <v>367</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BR9" t="n">
         <v>367</v>
       </c>
-      <c r="BJ9" t="n">
+      <c r="BS9" t="n">
         <v>367</v>
       </c>
-      <c r="BK9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>669</v>
-      </c>
       <c r="BT9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC9" t="n">
         <v>0.7</v>
       </c>
-      <c r="BU9" t="n">
+      <c r="CD9" t="n">
         <v>0.9</v>
       </c>
-      <c r="BV9" t="n">
+      <c r="CE9" t="n">
         <v>0.9</v>
       </c>
-      <c r="BW9" t="n">
+      <c r="CF9" t="n">
         <v>0.9</v>
       </c>
-      <c r="BX9" t="n">
+      <c r="CG9" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BY9" t="n">
+      <c r="CH9" t="n">
         <v>0.8125</v>
       </c>
-      <c r="BZ9" t="n">
+      <c r="CI9" t="n">
         <v>0.9375</v>
       </c>
-      <c r="CA9" t="n">
+      <c r="CJ9" t="n">
         <v>1</v>
       </c>
-      <c r="CB9" t="n">
+      <c r="CK9" t="n">
         <v>0.88</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>470.7</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>69.61</v>
       </c>
     </row>
     <row r="10">
@@ -2808,10 +3127,10 @@
         <v>478</v>
       </c>
       <c r="C10" t="n">
+        <v>87.47220163083766</v>
+      </c>
+      <c r="D10" t="n">
         <v>59</v>
-      </c>
-      <c r="D10" t="n">
-        <v>87.47220163083766</v>
       </c>
       <c r="E10" t="n">
         <v>478</v>
@@ -2820,228 +3139,261 @@
         <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>456.9918773267279</v>
-      </c>
-      <c r="J10" t="n">
-        <v>72.8979289676703</v>
-      </c>
-      <c r="K10" t="n">
-        <v>476.3955580306333</v>
-      </c>
-      <c r="L10" t="n">
-        <v>77.62919748382706</v>
-      </c>
-      <c r="M10" t="n">
-        <v>469.0336625880987</v>
-      </c>
-      <c r="N10" t="n">
-        <v>74.27944960312708</v>
-      </c>
-      <c r="O10" t="n">
-        <v>473.74693488969</v>
-      </c>
-      <c r="P10" t="n">
-        <v>72.40305257065351</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>468.7485628302464</v>
-      </c>
       <c r="R10" t="n">
-        <v>70.31433616466639</v>
+        <v>456.99</v>
       </c>
       <c r="S10" t="n">
-        <v>469.8993604891086</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>67.46348646520717</v>
+        <v>476.4</v>
       </c>
       <c r="U10" t="n">
-        <v>465.683269023223</v>
+        <v>77.63</v>
       </c>
       <c r="V10" t="n">
-        <v>70.09270861862666</v>
+        <v>469.03</v>
       </c>
       <c r="W10" t="n">
-        <v>467.2991687171055</v>
+        <v>74.28</v>
       </c>
       <c r="X10" t="n">
-        <v>68.43060192275821</v>
+        <v>473.75</v>
       </c>
       <c r="Y10" t="n">
-        <v>467.6794166570523</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>71.59597796526688</v>
+        <v>468.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>70.31</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>469.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>465.68</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>70.09</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>467.3</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>467.68</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
         <v>501.625</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AT10" t="n">
         <v>501.1666666666667</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AU10" t="n">
         <v>501.0125</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AV10" t="n">
         <v>500.39</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AW10" t="n">
         <v>500.2</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AX10" t="n">
         <v>500.2642857142857</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AY10" t="n">
         <v>501.275</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AZ10" t="n">
         <v>501.7277777777778</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="BA10" t="n">
         <v>502.71</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="BB10" t="n">
         <v>124.435261782985</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="BC10" t="n">
         <v>113.0421995932886</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="BD10" t="n">
         <v>102.3948843631849</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="BE10" t="n">
         <v>93.72853300889756</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="BF10" t="n">
         <v>86.47866788983281</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="BG10" t="n">
         <v>84.57892431791451</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="BH10" t="n">
         <v>86.36484744964238</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BI10" t="n">
         <v>85.67709602893072</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BJ10" t="n">
         <v>86.06117533475823</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BK10" t="n">
         <v>318</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BL10" t="n">
         <v>318</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BM10" t="n">
         <v>318</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BN10" t="n">
         <v>318</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BO10" t="n">
         <v>318</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BP10" t="n">
         <v>318</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BQ10" t="n">
         <v>318</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BR10" t="n">
         <v>318</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BS10" t="n">
         <v>318</v>
       </c>
-      <c r="BK10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>669</v>
-      </c>
       <c r="BT10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC10" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="BU10" t="n">
+      <c r="CD10" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="BV10" t="n">
+      <c r="CE10" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="BW10" t="n">
+      <c r="CF10" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="BX10" t="n">
+      <c r="CG10" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="BY10" t="n">
+      <c r="CH10" t="n">
         <v>0.9375</v>
       </c>
-      <c r="BZ10" t="n">
+      <c r="CI10" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CJ10" t="n">
         <v>0.8095238095238095</v>
       </c>
-      <c r="CB10" t="n">
+      <c r="CK10" t="n">
         <v>0.7037037037037037</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>467.68</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -3054,10 +3406,10 @@
         <v>480</v>
       </c>
       <c r="C11" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D11" t="n">
         <v>58</v>
-      </c>
-      <c r="D11" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E11" t="n">
         <v>480</v>
@@ -3066,228 +3418,261 @@
         <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>496.8166555771715</v>
-      </c>
-      <c r="J11" t="n">
-        <v>57.18292628093676</v>
-      </c>
-      <c r="K11" t="n">
-        <v>491.8844462469038</v>
-      </c>
-      <c r="L11" t="n">
-        <v>76.39133179698756</v>
-      </c>
-      <c r="M11" t="n">
-        <v>491.1133333610241</v>
-      </c>
-      <c r="N11" t="n">
-        <v>71.96428967017431</v>
-      </c>
-      <c r="O11" t="n">
-        <v>487.8810113136246</v>
-      </c>
-      <c r="P11" t="n">
-        <v>72.46679645875972</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>486.6367165799413</v>
-      </c>
       <c r="R11" t="n">
-        <v>74.93344589196028</v>
+        <v>496.82</v>
       </c>
       <c r="S11" t="n">
-        <v>492.1147339777115</v>
+        <v>57.18</v>
       </c>
       <c r="T11" t="n">
-        <v>81.25001468830064</v>
+        <v>491.88</v>
       </c>
       <c r="U11" t="n">
-        <v>491.4673292426054</v>
+        <v>76.39</v>
       </c>
       <c r="V11" t="n">
-        <v>76.86763714333996</v>
+        <v>491.11</v>
       </c>
       <c r="W11" t="n">
-        <v>486.9386242381854</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="X11" t="n">
-        <v>76.03704418048895</v>
+        <v>487.88</v>
       </c>
       <c r="Y11" t="n">
-        <v>485.3085561755605</v>
+        <v>72.47</v>
       </c>
       <c r="Z11" t="n">
-        <v>78.14406056732703</v>
+        <v>486.64</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>492.11</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>81.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>491.47</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>76.87</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>486.94</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>485.31</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>78.14</v>
       </c>
       <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
         <v>497.475</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AT11" t="n">
         <v>498.0166666666667</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AU11" t="n">
         <v>499.9</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AV11" t="n">
         <v>498.26</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AW11" t="n">
         <v>498.425</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AX11" t="n">
         <v>497.4142857142857</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AY11" t="n">
         <v>498.29375</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AZ11" t="n">
         <v>498.6166666666667</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="BA11" t="n">
         <v>497.965</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="BB11" t="n">
         <v>92.62936561911671</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="BC11" t="n">
         <v>86.5183008899787</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="BD11" t="n">
         <v>84.10597481748844</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="BE11" t="n">
         <v>85.85588156905735</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="BF11" t="n">
         <v>85.68145097783223</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="BG11" t="n">
         <v>86.55592624047725</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="BH11" t="n">
         <v>86.50004312679562</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BI11" t="n">
         <v>84.84098033641787</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BJ11" t="n">
         <v>86.79944570675552</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BK11" t="n">
         <v>365</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BL11" t="n">
         <v>365</v>
       </c>
-      <c r="BD11" t="n">
+      <c r="BM11" t="n">
         <v>365</v>
       </c>
-      <c r="BE11" t="n">
+      <c r="BN11" t="n">
         <v>365</v>
       </c>
-      <c r="BF11" t="n">
+      <c r="BO11" t="n">
         <v>365</v>
       </c>
-      <c r="BG11" t="n">
+      <c r="BP11" t="n">
         <v>365</v>
       </c>
-      <c r="BH11" t="n">
+      <c r="BQ11" t="n">
         <v>365</v>
       </c>
-      <c r="BI11" t="n">
+      <c r="BR11" t="n">
         <v>365</v>
       </c>
-      <c r="BJ11" t="n">
+      <c r="BS11" t="n">
         <v>365</v>
       </c>
-      <c r="BK11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>669</v>
-      </c>
       <c r="BT11" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC11" t="n">
         <v>0.8</v>
       </c>
-      <c r="BU11" t="n">
+      <c r="CD11" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BV11" t="n">
+      <c r="CE11" t="n">
         <v>0.9</v>
       </c>
-      <c r="BW11" t="n">
+      <c r="CF11" t="n">
         <v>0.9</v>
       </c>
-      <c r="BX11" t="n">
+      <c r="CG11" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="BY11" t="n">
+      <c r="CH11" t="n">
         <v>1</v>
       </c>
-      <c r="BZ11" t="n">
+      <c r="CI11" t="n">
         <v>0.9444444444444444</v>
       </c>
-      <c r="CA11" t="n">
+      <c r="CJ11" t="n">
         <v>0.9130434782608695</v>
       </c>
-      <c r="CB11" t="n">
+      <c r="CK11" t="n">
         <v>0.9629629629629629</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>485.31</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>78.14</v>
       </c>
     </row>
     <row r="12">
@@ -3300,10 +3685,10 @@
         <v>478</v>
       </c>
       <c r="C12" t="n">
+        <v>91.91994069681246</v>
+      </c>
+      <c r="D12" t="n">
         <v>62</v>
-      </c>
-      <c r="D12" t="n">
-        <v>91.91994069681246</v>
       </c>
       <c r="E12" t="n">
         <v>478</v>
@@ -3312,228 +3697,261 @@
         <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>493.5847013633633</v>
-      </c>
-      <c r="J12" t="n">
-        <v>26.19327758793246</v>
-      </c>
-      <c r="K12" t="n">
-        <v>485.5164808866519</v>
-      </c>
-      <c r="L12" t="n">
-        <v>38.76954135457555</v>
-      </c>
-      <c r="M12" t="n">
-        <v>491.7899096122371</v>
-      </c>
-      <c r="N12" t="n">
-        <v>39.87386909899142</v>
-      </c>
-      <c r="O12" t="n">
-        <v>493.2957442704278</v>
-      </c>
-      <c r="P12" t="n">
-        <v>38.60177600749052</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>486.5998326345327</v>
-      </c>
       <c r="R12" t="n">
-        <v>48.27833980459138</v>
+        <v>493.58</v>
       </c>
       <c r="S12" t="n">
-        <v>486.5617175571521</v>
+        <v>26.19</v>
       </c>
       <c r="T12" t="n">
-        <v>55.46037332801361</v>
+        <v>485.52</v>
       </c>
       <c r="U12" t="n">
-        <v>485.452845887005</v>
+        <v>38.77</v>
       </c>
       <c r="V12" t="n">
-        <v>59.30390315411246</v>
+        <v>491.79</v>
       </c>
       <c r="W12" t="n">
-        <v>485.0339205962242</v>
+        <v>39.87</v>
       </c>
       <c r="X12" t="n">
-        <v>69.01009227174022</v>
+        <v>493.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>480.1811468279446</v>
+        <v>38.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>73.93657532292998</v>
+        <v>486.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>48.28</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>486.56</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>55.46</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>485.45</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>59.3</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>485.03</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>480.18</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>73.94</v>
       </c>
       <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
         <v>502.65</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AT12" t="n">
         <v>502.8833333333333</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AU12" t="n">
         <v>502.5625</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AV12" t="n">
         <v>501.74</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AW12" t="n">
         <v>501.5833333333333</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AX12" t="n">
         <v>501.15</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AY12" t="n">
         <v>501.26875</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AZ12" t="n">
         <v>501.1611111111111</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="BA12" t="n">
         <v>500.885</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="BB12" t="n">
         <v>57.85566091576519</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="BC12" t="n">
         <v>50.41497517823669</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="BD12" t="n">
         <v>47.45230335558011</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="BE12" t="n">
         <v>45.66434495314698</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="BF12" t="n">
         <v>50.0515706269266</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="BG12" t="n">
         <v>56.52937605478108</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="BH12" t="n">
         <v>63.84930714923617</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BI12" t="n">
         <v>72.79218241671047</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BJ12" t="n">
         <v>81.17784041842945</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BK12" t="n">
         <v>320</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BL12" t="n">
         <v>320</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BM12" t="n">
         <v>320</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BN12" t="n">
         <v>320</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BO12" t="n">
         <v>320</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BP12" t="n">
         <v>320</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BQ12" t="n">
         <v>320</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BR12" t="n">
         <v>320</v>
       </c>
-      <c r="BJ12" t="n">
+      <c r="BS12" t="n">
         <v>320</v>
       </c>
-      <c r="BK12" t="n">
+      <c r="BT12" t="n">
         <v>640</v>
       </c>
-      <c r="BL12" t="n">
+      <c r="BU12" t="n">
         <v>640</v>
       </c>
-      <c r="BM12" t="n">
+      <c r="BV12" t="n">
         <v>640</v>
       </c>
-      <c r="BN12" t="n">
+      <c r="BW12" t="n">
         <v>640</v>
       </c>
-      <c r="BO12" t="n">
+      <c r="BX12" t="n">
         <v>640</v>
       </c>
-      <c r="BP12" t="n">
+      <c r="BY12" t="n">
         <v>640</v>
       </c>
-      <c r="BQ12" t="n">
+      <c r="BZ12" t="n">
         <v>640</v>
       </c>
-      <c r="BR12" t="n">
+      <c r="CA12" t="n">
         <v>640</v>
       </c>
-      <c r="BS12" t="n">
+      <c r="CB12" t="n">
         <v>640</v>
       </c>
-      <c r="BT12" t="n">
+      <c r="CC12" t="n">
         <v>0.7</v>
       </c>
-      <c r="BU12" t="n">
+      <c r="CD12" t="n">
         <v>0.75</v>
       </c>
-      <c r="BV12" t="n">
+      <c r="CE12" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="BW12" t="n">
+      <c r="CF12" t="n">
         <v>0.625</v>
       </c>
-      <c r="BX12" t="n">
+      <c r="CG12" t="n">
         <v>0.625</v>
       </c>
-      <c r="BY12" t="n">
+      <c r="CH12" t="n">
         <v>0.625</v>
       </c>
-      <c r="BZ12" t="n">
+      <c r="CI12" t="n">
         <v>0.625</v>
       </c>
-      <c r="CA12" t="n">
+      <c r="CJ12" t="n">
         <v>0.625</v>
       </c>
-      <c r="CB12" t="n">
+      <c r="CK12" t="n">
         <v>0.625</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>480.18</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>73.94</v>
       </c>
     </row>
     <row r="13">
@@ -3546,10 +3964,10 @@
         <v>480</v>
       </c>
       <c r="C13" t="n">
+        <v>91.91994069681246</v>
+      </c>
+      <c r="D13" t="n">
         <v>62</v>
-      </c>
-      <c r="D13" t="n">
-        <v>91.91994069681246</v>
       </c>
       <c r="E13" t="n">
         <v>480</v>
@@ -3558,228 +3976,261 @@
         <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>490.085365485925</v>
-      </c>
-      <c r="J13" t="n">
-        <v>65.77987791546086</v>
-      </c>
-      <c r="K13" t="n">
-        <v>487.1077458797875</v>
-      </c>
-      <c r="L13" t="n">
-        <v>71.63195037102521</v>
-      </c>
-      <c r="M13" t="n">
-        <v>484.3642535987029</v>
-      </c>
-      <c r="N13" t="n">
-        <v>65.97048193670481</v>
-      </c>
-      <c r="O13" t="n">
-        <v>480.3545086950179</v>
-      </c>
-      <c r="P13" t="n">
-        <v>76.62541039879785</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>482.5083959225981</v>
-      </c>
       <c r="R13" t="n">
-        <v>75.73582127388013</v>
+        <v>490.09</v>
       </c>
       <c r="S13" t="n">
-        <v>477.1252151896982</v>
+        <v>65.78</v>
       </c>
       <c r="T13" t="n">
-        <v>70.47797320985266</v>
+        <v>487.11</v>
       </c>
       <c r="U13" t="n">
-        <v>472.8329736130001</v>
+        <v>71.63</v>
       </c>
       <c r="V13" t="n">
-        <v>67.03421306342919</v>
+        <v>484.36</v>
       </c>
       <c r="W13" t="n">
-        <v>477.3137823692599</v>
+        <v>65.97</v>
       </c>
       <c r="X13" t="n">
-        <v>67.53611085830401</v>
+        <v>480.35</v>
       </c>
       <c r="Y13" t="n">
-        <v>476.739764974257</v>
+        <v>76.63</v>
       </c>
       <c r="Z13" t="n">
-        <v>67.6563520437759</v>
+        <v>482.51</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>477.13</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>70.48</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>472.83</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>67.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>477.31</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>476.74</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>67.66</v>
       </c>
       <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
         <v>497.4</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AT13" t="n">
         <v>497.8833333333333</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AU13" t="n">
         <v>499.4375</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AV13" t="n">
         <v>499.62</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AW13" t="n">
         <v>499.875</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AX13" t="n">
         <v>500.8071428571429</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AY13" t="n">
         <v>498.8875</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AZ13" t="n">
         <v>498.2111111111111</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="BA13" t="n">
         <v>498.95</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="BB13" t="n">
         <v>86.77407446927913</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="BC13" t="n">
         <v>83.36887741970754</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="BD13" t="n">
         <v>77.22157142761341</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="BE13" t="n">
         <v>76.67095669156608</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="BF13" t="n">
         <v>86.61260132528831</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="BG13" t="n">
         <v>83.52056174795449</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="BH13" t="n">
         <v>81.36115377592675</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BI13" t="n">
         <v>79.60555458627026</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BJ13" t="n">
         <v>79.85397610639059</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BK13" t="n">
         <v>327</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BL13" t="n">
         <v>327</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BM13" t="n">
         <v>327</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BN13" t="n">
         <v>327</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BO13" t="n">
         <v>327</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BP13" t="n">
         <v>327</v>
       </c>
-      <c r="BH13" t="n">
+      <c r="BQ13" t="n">
         <v>327</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BR13" t="n">
         <v>327</v>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BS13" t="n">
         <v>327</v>
       </c>
-      <c r="BK13" t="n">
+      <c r="BT13" t="n">
         <v>613</v>
       </c>
-      <c r="BL13" t="n">
+      <c r="BU13" t="n">
         <v>613</v>
       </c>
-      <c r="BM13" t="n">
+      <c r="BV13" t="n">
         <v>613</v>
       </c>
-      <c r="BN13" t="n">
+      <c r="BW13" t="n">
         <v>613</v>
       </c>
-      <c r="BO13" t="n">
+      <c r="BX13" t="n">
         <v>634</v>
       </c>
-      <c r="BP13" t="n">
+      <c r="BY13" t="n">
         <v>634</v>
       </c>
-      <c r="BQ13" t="n">
+      <c r="BZ13" t="n">
         <v>634</v>
       </c>
-      <c r="BR13" t="n">
+      <c r="CA13" t="n">
         <v>634</v>
       </c>
-      <c r="BS13" t="n">
+      <c r="CB13" t="n">
         <v>634</v>
       </c>
-      <c r="BT13" t="n">
+      <c r="CC13" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BU13" t="n">
+      <c r="CD13" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="BV13" t="n">
+      <c r="CE13" t="n">
         <v>0.9375</v>
       </c>
-      <c r="BW13" t="n">
+      <c r="CF13" t="n">
         <v>0.9375</v>
       </c>
-      <c r="BX13" t="n">
+      <c r="CG13" t="n">
         <v>0.8125</v>
       </c>
-      <c r="BY13" t="n">
+      <c r="CH13" t="n">
         <v>0.8125</v>
       </c>
-      <c r="BZ13" t="n">
+      <c r="CI13" t="n">
         <v>0.9375</v>
       </c>
-      <c r="CA13" t="n">
+      <c r="CJ13" t="n">
         <v>0.8421052631578947</v>
       </c>
-      <c r="CB13" t="n">
+      <c r="CK13" t="n">
         <v>0.7391304347826086</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>476.74</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>67.66</v>
       </c>
     </row>
     <row r="14">
@@ -3792,10 +4243,10 @@
         <v>479</v>
       </c>
       <c r="C14" t="n">
+        <v>90.43736100815418</v>
+      </c>
+      <c r="D14" t="n">
         <v>61</v>
-      </c>
-      <c r="D14" t="n">
-        <v>90.43736100815418</v>
       </c>
       <c r="E14" t="n">
         <v>479</v>
@@ -3804,228 +4255,261 @@
         <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>446.9729082688462</v>
-      </c>
-      <c r="J14" t="n">
-        <v>59.05932545470494</v>
-      </c>
-      <c r="K14" t="n">
-        <v>483.6512124326273</v>
-      </c>
-      <c r="L14" t="n">
-        <v>67.02570436853139</v>
-      </c>
-      <c r="M14" t="n">
-        <v>477.9456895289661</v>
-      </c>
-      <c r="N14" t="n">
-        <v>73.41916933059312</v>
-      </c>
-      <c r="O14" t="n">
-        <v>470.183641158794</v>
-      </c>
-      <c r="P14" t="n">
-        <v>68.98905277962554</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>472.2045403051594</v>
-      </c>
       <c r="R14" t="n">
-        <v>65.38322335572832</v>
+        <v>446.97</v>
       </c>
       <c r="S14" t="n">
-        <v>476.9449367875362</v>
+        <v>59.06</v>
       </c>
       <c r="T14" t="n">
-        <v>69.20406845384757</v>
+        <v>483.65</v>
       </c>
       <c r="U14" t="n">
-        <v>478.9478331159502</v>
+        <v>67.03</v>
       </c>
       <c r="V14" t="n">
-        <v>67.43428621269845</v>
+        <v>477.95</v>
       </c>
       <c r="W14" t="n">
-        <v>476.736430292121</v>
+        <v>73.42</v>
       </c>
       <c r="X14" t="n">
-        <v>65.35320336031685</v>
+        <v>470.18</v>
       </c>
       <c r="Y14" t="n">
-        <v>474.3298445968923</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="Z14" t="n">
-        <v>64.48785085052073</v>
+        <v>472.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>65.38</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>476.94</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>69.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>478.95</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>476.74</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>474.33</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
         <v>504.45</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AT14" t="n">
         <v>502.0833333333333</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AU14" t="n">
         <v>500.775</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AV14" t="n">
         <v>502.52</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AW14" t="n">
         <v>502.2083333333333</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AX14" t="n">
         <v>500.4857142857143</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AY14" t="n">
         <v>501.05</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AZ14" t="n">
         <v>501.0444444444444</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="BA14" t="n">
         <v>500.74</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="BB14" t="n">
         <v>95.99555979314877</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="BC14" t="n">
         <v>89.42264658475627</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="BD14" t="n">
         <v>87.59936857649147</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="BE14" t="n">
         <v>86.90989356799375</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="BF14" t="n">
         <v>80.72059793234659</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="BG14" t="n">
         <v>80.12316284626935</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="BH14" t="n">
         <v>79.19191877963307</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="BI14" t="n">
         <v>77.79808782441765</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BJ14" t="n">
         <v>77.40414975955747</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BK14" t="n">
         <v>342</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BL14" t="n">
         <v>342</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BM14" t="n">
         <v>342</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BN14" t="n">
         <v>342</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BO14" t="n">
         <v>342</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BP14" t="n">
         <v>342</v>
       </c>
-      <c r="BH14" t="n">
+      <c r="BQ14" t="n">
         <v>342</v>
       </c>
-      <c r="BI14" t="n">
+      <c r="BR14" t="n">
         <v>342</v>
       </c>
-      <c r="BJ14" t="n">
+      <c r="BS14" t="n">
         <v>342</v>
       </c>
-      <c r="BK14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>669</v>
-      </c>
       <c r="BT14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC14" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="BU14" t="n">
+      <c r="CD14" t="n">
         <v>0.2666666666666667</v>
       </c>
-      <c r="BV14" t="n">
+      <c r="CE14" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BW14" t="n">
+      <c r="CF14" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="BX14" t="n">
+      <c r="CG14" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="BY14" t="n">
+      <c r="CH14" t="n">
         <v>1</v>
       </c>
-      <c r="BZ14" t="n">
+      <c r="CI14" t="n">
         <v>0.9444444444444444</v>
       </c>
-      <c r="CA14" t="n">
+      <c r="CJ14" t="n">
         <v>1</v>
       </c>
-      <c r="CB14" t="n">
+      <c r="CK14" t="n">
         <v>0.84</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>474.33</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>64.48999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -4038,10 +4522,10 @@
         <v>479</v>
       </c>
       <c r="C15" t="n">
+        <v>90.43736100815418</v>
+      </c>
+      <c r="D15" t="n">
         <v>61</v>
-      </c>
-      <c r="D15" t="n">
-        <v>90.43736100815418</v>
       </c>
       <c r="E15" t="n">
         <v>479</v>
@@ -4050,228 +4534,261 @@
         <v>200</v>
       </c>
       <c r="G15" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>81.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>463.4135836314239</v>
-      </c>
-      <c r="J15" t="n">
-        <v>75.17911146312937</v>
-      </c>
-      <c r="K15" t="n">
-        <v>469.8878624860596</v>
-      </c>
-      <c r="L15" t="n">
-        <v>79.67065140147189</v>
-      </c>
-      <c r="M15" t="n">
-        <v>457.133022382769</v>
-      </c>
-      <c r="N15" t="n">
-        <v>74.00248051681821</v>
-      </c>
-      <c r="O15" t="n">
-        <v>458.9777341850079</v>
-      </c>
-      <c r="P15" t="n">
-        <v>65.57496306658641</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>466.4297901105581</v>
-      </c>
       <c r="R15" t="n">
-        <v>62.9024309535276</v>
+        <v>463.41</v>
       </c>
       <c r="S15" t="n">
-        <v>472.1786745282178</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>64.43567636446846</v>
+        <v>469.89</v>
       </c>
       <c r="U15" t="n">
-        <v>471.6486145320251</v>
+        <v>79.67</v>
       </c>
       <c r="V15" t="n">
-        <v>63.86771381015906</v>
+        <v>457.13</v>
       </c>
       <c r="W15" t="n">
-        <v>473.1334682215724</v>
+        <v>74</v>
       </c>
       <c r="X15" t="n">
-        <v>66.25983412306036</v>
+        <v>458.98</v>
       </c>
       <c r="Y15" t="n">
-        <v>472.7286513035112</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="Z15" t="n">
-        <v>65.47886839561667</v>
+        <v>466.43</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>62.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>472.18</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>64.44</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>471.65</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>63.87</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>473.13</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>472.73</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>65.48</v>
       </c>
       <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
         <v>497.75</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AT15" t="n">
         <v>497.95</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AU15" t="n">
         <v>498.5625</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AV15" t="n">
         <v>498.63</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AW15" t="n">
         <v>498.4833333333333</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AX15" t="n">
         <v>498.6857142857143</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AY15" t="n">
         <v>498.85625</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AZ15" t="n">
         <v>498.8777777777778</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="BA15" t="n">
         <v>498.975</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="BB15" t="n">
         <v>113.405412128346</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="BC15" t="n">
         <v>103.9075590769667</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="BD15" t="n">
         <v>100.8354902489694</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="BE15" t="n">
         <v>96.31839440106963</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="BF15" t="n">
         <v>92.8930373542005</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="BG15" t="n">
         <v>90.07259657110605</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="BH15" t="n">
         <v>87.91976789060296</v>
       </c>
-      <c r="AZ15" t="n">
+      <c r="BI15" t="n">
         <v>86.26095135340823</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BJ15" t="n">
         <v>84.60138518369543</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BK15" t="n">
         <v>318</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BL15" t="n">
         <v>318</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BM15" t="n">
         <v>318</v>
       </c>
-      <c r="BE15" t="n">
+      <c r="BN15" t="n">
         <v>318</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="BO15" t="n">
         <v>318</v>
       </c>
-      <c r="BG15" t="n">
+      <c r="BP15" t="n">
         <v>318</v>
       </c>
-      <c r="BH15" t="n">
+      <c r="BQ15" t="n">
         <v>318</v>
       </c>
-      <c r="BI15" t="n">
+      <c r="BR15" t="n">
         <v>318</v>
       </c>
-      <c r="BJ15" t="n">
+      <c r="BS15" t="n">
         <v>318</v>
       </c>
-      <c r="BK15" t="n">
+      <c r="BT15" t="n">
         <v>684</v>
       </c>
-      <c r="BL15" t="n">
+      <c r="BU15" t="n">
         <v>684</v>
       </c>
-      <c r="BM15" t="n">
+      <c r="BV15" t="n">
         <v>684</v>
       </c>
-      <c r="BN15" t="n">
+      <c r="BW15" t="n">
         <v>684</v>
       </c>
-      <c r="BO15" t="n">
+      <c r="BX15" t="n">
         <v>684</v>
       </c>
-      <c r="BP15" t="n">
+      <c r="BY15" t="n">
         <v>684</v>
       </c>
-      <c r="BQ15" t="n">
+      <c r="BZ15" t="n">
         <v>684</v>
       </c>
-      <c r="BR15" t="n">
+      <c r="CA15" t="n">
         <v>684</v>
       </c>
-      <c r="BS15" t="n">
+      <c r="CB15" t="n">
         <v>684</v>
       </c>
-      <c r="BT15" t="n">
+      <c r="CC15" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BU15" t="n">
+      <c r="CD15" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BV15" t="n">
+      <c r="CE15" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="BW15" t="n">
+      <c r="CF15" t="n">
         <v>0.8095238095238095</v>
       </c>
-      <c r="BX15" t="n">
+      <c r="CG15" t="n">
         <v>0.8846153846153846</v>
       </c>
-      <c r="BY15" t="n">
+      <c r="CH15" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="BZ15" t="n">
+      <c r="CI15" t="n">
         <v>0.7674418604651163</v>
       </c>
-      <c r="CA15" t="n">
+      <c r="CJ15" t="n">
         <v>0.6981132075471698</v>
       </c>
-      <c r="CB15" t="n">
+      <c r="CK15" t="n">
         <v>0.6507936507936508</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>472.73</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>65.48</v>
       </c>
     </row>
     <row r="16">
@@ -4284,10 +4801,10 @@
         <v>478</v>
       </c>
       <c r="C16" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D16" t="n">
         <v>58</v>
-      </c>
-      <c r="D16" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E16" t="n">
         <v>478</v>
@@ -4296,228 +4813,261 @@
         <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>475.0283696411117</v>
-      </c>
-      <c r="J16" t="n">
-        <v>84.95255512108</v>
-      </c>
-      <c r="K16" t="n">
-        <v>480.6408279443183</v>
-      </c>
-      <c r="L16" t="n">
-        <v>71.72057690718925</v>
-      </c>
-      <c r="M16" t="n">
-        <v>478.8912152485001</v>
-      </c>
-      <c r="N16" t="n">
-        <v>75.60810668327404</v>
-      </c>
-      <c r="O16" t="n">
-        <v>470.4497897591801</v>
-      </c>
-      <c r="P16" t="n">
-        <v>73.97723663833813</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>477.9515357733234</v>
-      </c>
       <c r="R16" t="n">
-        <v>75.14072978632134</v>
+        <v>475.03</v>
       </c>
       <c r="S16" t="n">
-        <v>474.4507586740165</v>
+        <v>84.95</v>
       </c>
       <c r="T16" t="n">
-        <v>70.58691766022341</v>
+        <v>480.64</v>
       </c>
       <c r="U16" t="n">
-        <v>469.4097706346035</v>
+        <v>71.72</v>
       </c>
       <c r="V16" t="n">
-        <v>74.42161574512981</v>
+        <v>478.89</v>
       </c>
       <c r="W16" t="n">
-        <v>470.9531266125797</v>
+        <v>75.61</v>
       </c>
       <c r="X16" t="n">
-        <v>74.79232592835274</v>
+        <v>470.45</v>
       </c>
       <c r="Y16" t="n">
-        <v>469.1861225102654</v>
+        <v>73.98</v>
       </c>
       <c r="Z16" t="n">
-        <v>71.03318568281367</v>
+        <v>477.95</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>75.14</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>474.45</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>70.59</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>469.41</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>74.42</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>470.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>469.19</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>71.03</v>
       </c>
       <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
         <v>496.475</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AT16" t="n">
         <v>498.1833333333333</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AU16" t="n">
         <v>501.1</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AV16" t="n">
         <v>499.2</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AW16" t="n">
         <v>498.9166666666667</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AX16" t="n">
         <v>499.3928571428572</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AY16" t="n">
         <v>498.46875</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AZ16" t="n">
         <v>498.7277777777778</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="BA16" t="n">
         <v>499.065</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="BB16" t="n">
         <v>102.229151297465</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="BC16" t="n">
         <v>90.50478655236357</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="BD16" t="n">
         <v>88.7918352102264</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="BE16" t="n">
         <v>89.8042315261369</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="BF16" t="n">
         <v>90.00996086853696</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="BG16" t="n">
         <v>88.20379781494441</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="BH16" t="n">
         <v>88.97232167049199</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="BI16" t="n">
         <v>88.4442593172267</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BJ16" t="n">
         <v>88.03295277905882</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BK16" t="n">
         <v>347</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BL16" t="n">
         <v>347</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BM16" t="n">
         <v>347</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BN16" t="n">
         <v>347</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="BO16" t="n">
         <v>347</v>
       </c>
-      <c r="BG16" t="n">
+      <c r="BP16" t="n">
         <v>347</v>
       </c>
-      <c r="BH16" t="n">
+      <c r="BQ16" t="n">
         <v>347</v>
       </c>
-      <c r="BI16" t="n">
+      <c r="BR16" t="n">
         <v>347</v>
       </c>
-      <c r="BJ16" t="n">
+      <c r="BS16" t="n">
         <v>347</v>
       </c>
-      <c r="BK16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>669</v>
-      </c>
       <c r="BT16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC16" t="n">
         <v>1</v>
       </c>
-      <c r="BU16" t="n">
+      <c r="CD16" t="n">
         <v>1</v>
       </c>
-      <c r="BV16" t="n">
+      <c r="CE16" t="n">
         <v>0.875</v>
       </c>
-      <c r="BW16" t="n">
+      <c r="CF16" t="n">
         <v>0.9</v>
       </c>
-      <c r="BX16" t="n">
+      <c r="CG16" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="BY16" t="n">
+      <c r="CH16" t="n">
         <v>0.875</v>
       </c>
-      <c r="BZ16" t="n">
+      <c r="CI16" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="CA16" t="n">
+      <c r="CJ16" t="n">
         <v>0.9047619047619048</v>
       </c>
-      <c r="CB16" t="n">
+      <c r="CK16" t="n">
         <v>0.9565217391304348</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>469.19</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>71.03</v>
       </c>
     </row>
     <row r="17">
@@ -4530,10 +5080,10 @@
         <v>482</v>
       </c>
       <c r="C17" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D17" t="n">
         <v>60</v>
-      </c>
-      <c r="D17" t="n">
-        <v>88.95478131949592</v>
       </c>
       <c r="E17" t="n">
         <v>482</v>
@@ -4542,228 +5092,261 @@
         <v>200</v>
       </c>
       <c r="G17" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>76</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="L17" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>459.2775544210517</v>
-      </c>
-      <c r="J17" t="n">
-        <v>49.64117085836429</v>
-      </c>
-      <c r="K17" t="n">
-        <v>447.4988650796492</v>
-      </c>
-      <c r="L17" t="n">
-        <v>77.79847179445538</v>
-      </c>
-      <c r="M17" t="n">
-        <v>450.8998826476845</v>
-      </c>
-      <c r="N17" t="n">
-        <v>90.95763642164999</v>
-      </c>
-      <c r="O17" t="n">
-        <v>464.2180817970007</v>
-      </c>
-      <c r="P17" t="n">
-        <v>76.26874530226044</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>475.8897239135893</v>
-      </c>
       <c r="R17" t="n">
-        <v>79.74607107535125</v>
+        <v>459.28</v>
       </c>
       <c r="S17" t="n">
-        <v>474.7504904416574</v>
+        <v>49.64</v>
       </c>
       <c r="T17" t="n">
-        <v>79.2954949253333</v>
+        <v>447.5</v>
       </c>
       <c r="U17" t="n">
-        <v>473.8240243629116</v>
+        <v>77.8</v>
       </c>
       <c r="V17" t="n">
-        <v>76.09566355119402</v>
+        <v>450.9</v>
       </c>
       <c r="W17" t="n">
-        <v>474.5887737904707</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>74.36686729712537</v>
+        <v>464.22</v>
       </c>
       <c r="Y17" t="n">
-        <v>471.6747451411426</v>
+        <v>76.27</v>
       </c>
       <c r="Z17" t="n">
-        <v>75.62434167584691</v>
+        <v>475.89</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>79.75</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>474.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>79.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>473.82</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>474.59</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>74.37</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>471.67</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>75.62</v>
       </c>
       <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
         <v>500.975</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AT17" t="n">
         <v>502.0333333333334</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AU17" t="n">
         <v>501.6625</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AV17" t="n">
         <v>501.96</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AW17" t="n">
         <v>499.6166666666667</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AX17" t="n">
         <v>499.9571428571429</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AY17" t="n">
         <v>499.875</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AZ17" t="n">
         <v>499.2333333333333</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="BA17" t="n">
         <v>499.41</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="BB17" t="n">
         <v>82.6103769208203</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="BC17" t="n">
         <v>84.88363930830383</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="BD17" t="n">
         <v>93.54904378853907</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="BE17" t="n">
         <v>90.87661085229797</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="BF17" t="n">
         <v>86.13566657056504</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="BG17" t="n">
         <v>85.3209797871352</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="BH17" t="n">
         <v>84.57871703330572</v>
       </c>
-      <c r="AZ17" t="n">
+      <c r="BI17" t="n">
         <v>83.51740337598306</v>
       </c>
-      <c r="BA17" t="n">
+      <c r="BJ17" t="n">
         <v>84.0480927802648</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="BK17" t="n">
         <v>329</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BL17" t="n">
         <v>329</v>
       </c>
-      <c r="BD17" t="n">
+      <c r="BM17" t="n">
         <v>329</v>
       </c>
-      <c r="BE17" t="n">
+      <c r="BN17" t="n">
         <v>329</v>
       </c>
-      <c r="BF17" t="n">
+      <c r="BO17" t="n">
         <v>329</v>
       </c>
-      <c r="BG17" t="n">
+      <c r="BP17" t="n">
         <v>329</v>
       </c>
-      <c r="BH17" t="n">
+      <c r="BQ17" t="n">
         <v>329</v>
       </c>
-      <c r="BI17" t="n">
+      <c r="BR17" t="n">
         <v>329</v>
       </c>
-      <c r="BJ17" t="n">
+      <c r="BS17" t="n">
         <v>329</v>
       </c>
-      <c r="BK17" t="n">
+      <c r="BT17" t="n">
         <v>633</v>
       </c>
-      <c r="BL17" t="n">
+      <c r="BU17" t="n">
         <v>633</v>
       </c>
-      <c r="BM17" t="n">
+      <c r="BV17" t="n">
         <v>636</v>
       </c>
-      <c r="BN17" t="n">
+      <c r="BW17" t="n">
         <v>636</v>
       </c>
-      <c r="BO17" t="n">
+      <c r="BX17" t="n">
         <v>636</v>
       </c>
-      <c r="BP17" t="n">
+      <c r="BY17" t="n">
         <v>636</v>
       </c>
-      <c r="BQ17" t="n">
+      <c r="BZ17" t="n">
         <v>636</v>
       </c>
-      <c r="BR17" t="n">
+      <c r="CA17" t="n">
         <v>636</v>
       </c>
-      <c r="BS17" t="n">
+      <c r="CB17" t="n">
         <v>636</v>
       </c>
-      <c r="BT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU17" t="n">
+      <c r="CC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD17" t="n">
         <v>1</v>
       </c>
-      <c r="BV17" t="n">
+      <c r="CE17" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="BW17" t="n">
+      <c r="CF17" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="BX17" t="n">
+      <c r="CG17" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="BY17" t="n">
+      <c r="CH17" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="BZ17" t="n">
+      <c r="CI17" t="n">
         <v>0.8823529411764706</v>
       </c>
-      <c r="CA17" t="n">
+      <c r="CJ17" t="n">
         <v>0.72</v>
       </c>
-      <c r="CB17" t="n">
+      <c r="CK17" t="n">
         <v>0.75</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>471.67</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>75.62</v>
       </c>
     </row>
     <row r="18">
@@ -4776,10 +5359,10 @@
         <v>482</v>
       </c>
       <c r="C18" t="n">
+        <v>87.47220163083766</v>
+      </c>
+      <c r="D18" t="n">
         <v>59</v>
-      </c>
-      <c r="D18" t="n">
-        <v>87.47220163083766</v>
       </c>
       <c r="E18" t="n">
         <v>482</v>
@@ -4788,228 +5371,261 @@
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>472.6160906422296</v>
-      </c>
-      <c r="J18" t="n">
-        <v>104.9966716868851</v>
-      </c>
-      <c r="K18" t="n">
-        <v>468.7578179782706</v>
-      </c>
-      <c r="L18" t="n">
-        <v>97.65928254084876</v>
-      </c>
-      <c r="M18" t="n">
-        <v>467.6693648439386</v>
-      </c>
-      <c r="N18" t="n">
-        <v>91.1678497751101</v>
-      </c>
-      <c r="O18" t="n">
-        <v>457.228746659855</v>
-      </c>
-      <c r="P18" t="n">
-        <v>93.29889498466795</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>468.2202320980848</v>
-      </c>
       <c r="R18" t="n">
-        <v>90.78536096715983</v>
+        <v>472.62</v>
       </c>
       <c r="S18" t="n">
-        <v>467.7467341712756</v>
+        <v>105</v>
       </c>
       <c r="T18" t="n">
-        <v>89.01004080378434</v>
+        <v>468.76</v>
       </c>
       <c r="U18" t="n">
-        <v>467.9166461972172</v>
+        <v>97.66</v>
       </c>
       <c r="V18" t="n">
-        <v>84.15907858763875</v>
+        <v>467.67</v>
       </c>
       <c r="W18" t="n">
-        <v>467.8656525623045</v>
+        <v>91.17</v>
       </c>
       <c r="X18" t="n">
-        <v>83.11636738217869</v>
+        <v>457.23</v>
       </c>
       <c r="Y18" t="n">
-        <v>472.2682564816389</v>
+        <v>93.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>84.67637103227722</v>
+        <v>468.22</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>90.79000000000001</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>467.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>467.92</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>84.16</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>467.87</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>83.12</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>472.27</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
         <v>504.925</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AT18" t="n">
         <v>504.2666666666667</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AU18" t="n">
         <v>503.7875</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AV18" t="n">
         <v>502.96</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AW18" t="n">
         <v>503.1083333333333</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="AX18" t="n">
         <v>503.5571428571429</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="AY18" t="n">
         <v>502.75</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AZ18" t="n">
         <v>502.0666666666667</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="BA18" t="n">
         <v>501.7</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="BB18" t="n">
         <v>90.97675183803827</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="BC18" t="n">
         <v>93.61888460965316</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="BD18" t="n">
         <v>91.93798096407164</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="BE18" t="n">
         <v>92.12772872485243</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="BF18" t="n">
         <v>94.26821626201603</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="BG18" t="n">
         <v>94.96557808178794</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="BH18" t="n">
         <v>91.00034340594546</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="BI18" t="n">
         <v>88.21467502002652</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BJ18" t="n">
         <v>90.36287954685818</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BK18" t="n">
         <v>379</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BL18" t="n">
         <v>379</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BM18" t="n">
         <v>379</v>
       </c>
-      <c r="BE18" t="n">
+      <c r="BN18" t="n">
         <v>379</v>
       </c>
-      <c r="BF18" t="n">
+      <c r="BO18" t="n">
         <v>359</v>
       </c>
-      <c r="BG18" t="n">
+      <c r="BP18" t="n">
         <v>359</v>
       </c>
-      <c r="BH18" t="n">
+      <c r="BQ18" t="n">
         <v>359</v>
       </c>
-      <c r="BI18" t="n">
+      <c r="BR18" t="n">
         <v>349</v>
       </c>
-      <c r="BJ18" t="n">
+      <c r="BS18" t="n">
         <v>349</v>
       </c>
-      <c r="BK18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>669</v>
-      </c>
       <c r="BT18" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BU18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD18" t="n">
         <v>0.6923076923076923</v>
       </c>
-      <c r="BV18" t="n">
+      <c r="CE18" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BW18" t="n">
+      <c r="CF18" t="n">
         <v>0.8823529411764706</v>
       </c>
-      <c r="BX18" t="n">
+      <c r="CG18" t="n">
         <v>0.85</v>
       </c>
-      <c r="BY18" t="n">
+      <c r="CH18" t="n">
         <v>0.8095238095238095</v>
       </c>
-      <c r="BZ18" t="n">
+      <c r="CI18" t="n">
         <v>0.7727272727272727</v>
       </c>
-      <c r="CA18" t="n">
+      <c r="CJ18" t="n">
         <v>0.7916666666666666</v>
       </c>
-      <c r="CB18" t="n">
+      <c r="CK18" t="n">
         <v>0.7916666666666666</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>472.27</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>84.68000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -5022,10 +5638,10 @@
         <v>479</v>
       </c>
       <c r="C19" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D19" t="n">
         <v>60</v>
-      </c>
-      <c r="D19" t="n">
-        <v>88.95478131949592</v>
       </c>
       <c r="E19" t="n">
         <v>479</v>
@@ -5034,228 +5650,261 @@
         <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>506.872337344486</v>
-      </c>
-      <c r="J19" t="n">
-        <v>69.31964698945866</v>
-      </c>
-      <c r="K19" t="n">
-        <v>487.9735088416131</v>
-      </c>
-      <c r="L19" t="n">
-        <v>73.29185187688879</v>
-      </c>
-      <c r="M19" t="n">
-        <v>490.4314284423163</v>
-      </c>
-      <c r="N19" t="n">
-        <v>82.48782009753285</v>
-      </c>
-      <c r="O19" t="n">
-        <v>484.5738548424221</v>
-      </c>
-      <c r="P19" t="n">
-        <v>85.1868419003498</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>481.7443630365632</v>
-      </c>
       <c r="R19" t="n">
-        <v>76.467440319514</v>
+        <v>506.87</v>
       </c>
       <c r="S19" t="n">
-        <v>479.1329281423828</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>75.44939934047845</v>
+        <v>487.97</v>
       </c>
       <c r="U19" t="n">
-        <v>485.9299435046323</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>76.91945814749417</v>
+        <v>490.43</v>
       </c>
       <c r="W19" t="n">
-        <v>479.3679651253464</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>79.67315383735333</v>
+        <v>484.57</v>
       </c>
       <c r="Y19" t="n">
-        <v>487.0516785344626</v>
+        <v>85.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>78.52035998909891</v>
+        <v>481.74</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>76.47</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>479.13</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>75.45</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>485.93</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>76.92</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>479.37</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>79.67</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>487.05</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>78.52</v>
       </c>
       <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
         <v>500.075</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AT19" t="n">
         <v>499.7666666666667</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AU19" t="n">
         <v>499.5875</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AV19" t="n">
         <v>499.81</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AW19" t="n">
         <v>500.525</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AX19" t="n">
         <v>500.5142857142857</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AY19" t="n">
         <v>500.0875</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AZ19" t="n">
         <v>500.3722222222222</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="BA19" t="n">
         <v>500.185</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="BB19" t="n">
         <v>77.61745534994044</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="BC19" t="n">
         <v>76.2959952349328</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="BD19" t="n">
         <v>76.68224920899229</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="BE19" t="n">
         <v>83.46708273325478</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="BF19" t="n">
         <v>85.47942856812587</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="BG19" t="n">
         <v>85.40696573417398</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="BH19" t="n">
         <v>85.28616443333584</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BI19" t="n">
         <v>85.66576073162716</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BJ19" t="n">
         <v>85.05933678909095</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BK19" t="n">
         <v>375</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BL19" t="n">
         <v>375</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BM19" t="n">
         <v>375</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BN19" t="n">
         <v>373</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BO19" t="n">
         <v>373</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BP19" t="n">
         <v>373</v>
       </c>
-      <c r="BH19" t="n">
+      <c r="BQ19" t="n">
         <v>373</v>
       </c>
-      <c r="BI19" t="n">
+      <c r="BR19" t="n">
         <v>373</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BS19" t="n">
         <v>373</v>
       </c>
-      <c r="BK19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>669</v>
-      </c>
       <c r="BT19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC19" t="n">
         <v>0.9</v>
       </c>
-      <c r="BU19" t="n">
+      <c r="CD19" t="n">
         <v>0.65</v>
       </c>
-      <c r="BV19" t="n">
+      <c r="CE19" t="n">
         <v>0.5862068965517241</v>
       </c>
-      <c r="BW19" t="n">
+      <c r="CF19" t="n">
         <v>0.5862068965517241</v>
       </c>
-      <c r="BX19" t="n">
+      <c r="CG19" t="n">
         <v>0.6896551724137931</v>
       </c>
-      <c r="BY19" t="n">
+      <c r="CH19" t="n">
         <v>0.8709677419354839</v>
       </c>
-      <c r="BZ19" t="n">
+      <c r="CI19" t="n">
         <v>0.9696969696969697</v>
       </c>
-      <c r="CA19" t="n">
+      <c r="CJ19" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="CB19" t="n">
+      <c r="CK19" t="n">
         <v>0.9166666666666666</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>487.05</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>78.52</v>
       </c>
     </row>
     <row r="20">
@@ -5268,10 +5917,10 @@
         <v>481</v>
       </c>
       <c r="C20" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D20" t="n">
         <v>60</v>
-      </c>
-      <c r="D20" t="n">
-        <v>88.95478131949592</v>
       </c>
       <c r="E20" t="n">
         <v>481</v>
@@ -5280,228 +5929,261 @@
         <v>200</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H20" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>504.3063650399525</v>
-      </c>
-      <c r="J20" t="n">
-        <v>59.72475279736292</v>
-      </c>
-      <c r="K20" t="n">
-        <v>502.2496664390188</v>
-      </c>
-      <c r="L20" t="n">
-        <v>71.57081043526343</v>
-      </c>
-      <c r="M20" t="n">
-        <v>500.6248378612091</v>
-      </c>
-      <c r="N20" t="n">
-        <v>72.73380333454828</v>
-      </c>
-      <c r="O20" t="n">
-        <v>497.2291704517249</v>
-      </c>
-      <c r="P20" t="n">
-        <v>79.19840428980336</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>491.7093354283916</v>
-      </c>
       <c r="R20" t="n">
-        <v>82.24705662895842</v>
+        <v>504.31</v>
       </c>
       <c r="S20" t="n">
-        <v>493.3409878421508</v>
+        <v>59.72</v>
       </c>
       <c r="T20" t="n">
-        <v>78.0968450947753</v>
+        <v>502.25</v>
       </c>
       <c r="U20" t="n">
-        <v>492.2423979404432</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>75.11756849298217</v>
+        <v>500.62</v>
       </c>
       <c r="W20" t="n">
-        <v>496.4764294821176</v>
+        <v>72.73</v>
       </c>
       <c r="X20" t="n">
-        <v>73.70256592915405</v>
+        <v>497.23</v>
       </c>
       <c r="Y20" t="n">
-        <v>500.6037780342217</v>
+        <v>79.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>71.84896588895393</v>
+        <v>491.71</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>82.25</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>493.34</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>492.24</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>75.12</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>496.48</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>73.7</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>500.6</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
         <v>495.35</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AT20" t="n">
         <v>496.3666666666667</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AU20" t="n">
         <v>496.1875</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AV20" t="n">
         <v>497.37</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AW20" t="n">
         <v>498.375</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AX20" t="n">
         <v>498.6142857142857</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AY20" t="n">
         <v>498.64375</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AZ20" t="n">
         <v>498.1888888888889</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="BA20" t="n">
         <v>500.68</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="BB20" t="n">
         <v>86.60298782374659</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="BC20" t="n">
         <v>82.64219395818472</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="BD20" t="n">
         <v>81.73066954179441</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="BE20" t="n">
         <v>85.0532368578645</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="BF20" t="n">
         <v>90.49033673087236</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="BG20" t="n">
         <v>86.35297874871202</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="BH20" t="n">
         <v>81.35465159373187</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BI20" t="n">
         <v>77.40892777170752</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BJ20" t="n">
         <v>75.95951289996533</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BK20" t="n">
         <v>346</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BL20" t="n">
         <v>346</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BM20" t="n">
         <v>346</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BN20" t="n">
         <v>346</v>
       </c>
-      <c r="BF20" t="n">
+      <c r="BO20" t="n">
         <v>346</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BP20" t="n">
         <v>346</v>
       </c>
-      <c r="BH20" t="n">
+      <c r="BQ20" t="n">
         <v>346</v>
       </c>
-      <c r="BI20" t="n">
+      <c r="BR20" t="n">
         <v>346</v>
       </c>
-      <c r="BJ20" t="n">
+      <c r="BS20" t="n">
         <v>346</v>
       </c>
-      <c r="BK20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>669</v>
-      </c>
       <c r="BT20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC20" t="n">
         <v>1</v>
       </c>
-      <c r="BU20" t="n">
+      <c r="CD20" t="n">
         <v>1</v>
       </c>
-      <c r="BV20" t="n">
+      <c r="CE20" t="n">
         <v>0.9375</v>
       </c>
-      <c r="BW20" t="n">
+      <c r="CF20" t="n">
         <v>0.3529411764705883</v>
       </c>
-      <c r="BX20" t="n">
+      <c r="CG20" t="n">
         <v>0.8235294117647058</v>
       </c>
-      <c r="BY20" t="n">
+      <c r="CH20" t="n">
         <v>0.8823529411764706</v>
       </c>
-      <c r="BZ20" t="n">
+      <c r="CI20" t="n">
         <v>0.8823529411764706</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CJ20" t="n">
         <v>0.8823529411764706</v>
       </c>
-      <c r="CB20" t="n">
+      <c r="CK20" t="n">
         <v>0.8947368421052632</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>500.6</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>71.84999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -5514,10 +6196,10 @@
         <v>482</v>
       </c>
       <c r="C21" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D21" t="n">
         <v>58</v>
-      </c>
-      <c r="D21" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E21" t="n">
         <v>482</v>
@@ -5526,228 +6208,261 @@
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>455.2743427367467</v>
-      </c>
-      <c r="J21" t="n">
-        <v>57.27101765461843</v>
-      </c>
-      <c r="K21" t="n">
-        <v>461.5622534816308</v>
-      </c>
-      <c r="L21" t="n">
-        <v>54.34790522466676</v>
-      </c>
-      <c r="M21" t="n">
-        <v>472.3421456844438</v>
-      </c>
-      <c r="N21" t="n">
-        <v>63.15575538744444</v>
-      </c>
-      <c r="O21" t="n">
-        <v>467.2292748722879</v>
-      </c>
-      <c r="P21" t="n">
-        <v>71.31933952690179</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>474.5428257103067</v>
-      </c>
       <c r="R21" t="n">
-        <v>72.99792319793416</v>
+        <v>455.27</v>
       </c>
       <c r="S21" t="n">
-        <v>481.1181698207569</v>
+        <v>57.27</v>
       </c>
       <c r="T21" t="n">
-        <v>66.8397544835064</v>
+        <v>461.56</v>
       </c>
       <c r="U21" t="n">
-        <v>487.3722115468084</v>
+        <v>54.35</v>
       </c>
       <c r="V21" t="n">
-        <v>64.52143058599286</v>
+        <v>472.34</v>
       </c>
       <c r="W21" t="n">
-        <v>481.6735101724515</v>
+        <v>63.16</v>
       </c>
       <c r="X21" t="n">
-        <v>63.10289241995523</v>
+        <v>467.23</v>
       </c>
       <c r="Y21" t="n">
-        <v>482.9049967773828</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="Z21" t="n">
-        <v>62.18520726017846</v>
+        <v>474.54</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>481.12</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>66.84</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>487.37</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>64.52</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>481.67</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>63.1</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>482.9</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>62.19</v>
       </c>
       <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
         <v>497.5</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AT21" t="n">
         <v>497.5333333333334</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AU21" t="n">
         <v>498.4625</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AV21" t="n">
         <v>498.8</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AW21" t="n">
         <v>499.2583333333333</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AX21" t="n">
         <v>499.7285714285715</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AY21" t="n">
         <v>498.88125</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AZ21" t="n">
         <v>499.7611111111111</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="BA21" t="n">
         <v>499.995</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="BB21" t="n">
         <v>100.9757396605739</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="BC21" t="n">
         <v>90.09392629670191</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="BD21" t="n">
         <v>83.80273619488804</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="BE21" t="n">
         <v>81.71340159361866</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="BF21" t="n">
         <v>84.30949885524301</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="BG21" t="n">
         <v>84.4455735841683</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BH21" t="n">
         <v>80.90189829934462</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BI21" t="n">
         <v>77.54019487328912</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BJ21" t="n">
         <v>75.12552811794403</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BK21" t="n">
         <v>281</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BL21" t="n">
         <v>281</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BM21" t="n">
         <v>281</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BN21" t="n">
         <v>281</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BO21" t="n">
         <v>281</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BP21" t="n">
         <v>281</v>
       </c>
-      <c r="BH21" t="n">
+      <c r="BQ21" t="n">
         <v>281</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BR21" t="n">
         <v>281</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BS21" t="n">
         <v>281</v>
       </c>
-      <c r="BK21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>669</v>
-      </c>
       <c r="BT21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC21" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="BU21" t="n">
+      <c r="CD21" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BV21" t="n">
+      <c r="CE21" t="n">
         <v>0.6428571428571429</v>
       </c>
-      <c r="BW21" t="n">
+      <c r="CF21" t="n">
         <v>0.6060606060606061</v>
       </c>
-      <c r="BX21" t="n">
+      <c r="CG21" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="BY21" t="n">
+      <c r="CH21" t="n">
         <v>0.8484848484848485</v>
       </c>
-      <c r="BZ21" t="n">
+      <c r="CI21" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="CA21" t="n">
+      <c r="CJ21" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="CB21" t="n">
+      <c r="CK21" t="n">
         <v>0.9090909090909091</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>482.9</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>62.19</v>
       </c>
     </row>
     <row r="22">
@@ -5760,10 +6475,10 @@
         <v>479.65</v>
       </c>
       <c r="C22" t="n">
+        <v>88.36174944403261</v>
+      </c>
+      <c r="D22" t="n">
         <v>59.6</v>
-      </c>
-      <c r="D22" t="n">
-        <v>88.3617494440326</v>
       </c>
       <c r="E22" t="n">
         <v>479.65</v>
@@ -5772,224 +6487,239 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.56375</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>77.47499999999999</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.66</v>
+      </c>
       <c r="I22" t="n">
-        <v>478.0639633757651</v>
+        <v>2.756</v>
       </c>
       <c r="J22" t="n">
-        <v>62.3745442607703</v>
+        <v>2.8005</v>
       </c>
       <c r="K22" t="n">
-        <v>477.2207891234469</v>
+        <v>2.837</v>
       </c>
       <c r="L22" t="n">
-        <v>69.711085907141</v>
+        <v>2.875</v>
       </c>
       <c r="M22" t="n">
-        <v>478.1515534021843</v>
+        <v>2.891</v>
       </c>
       <c r="N22" t="n">
-        <v>70.1059377192603</v>
+        <v>2.541</v>
       </c>
       <c r="O22" t="n">
-        <v>476.6145779060774</v>
+        <v>2.537999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>69.78365283880555</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>478.0422165057283</v>
-      </c>
+        <v>2.5755</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>68.80322063304385</v>
+        <v>478.064</v>
       </c>
       <c r="S22" t="n">
-        <v>478.2840768350528</v>
+        <v>62.3735</v>
       </c>
       <c r="T22" t="n">
-        <v>68.83042251707792</v>
+        <v>477.221</v>
       </c>
       <c r="U22" t="n">
-        <v>478.1193691405023</v>
+        <v>69.7115</v>
       </c>
       <c r="V22" t="n">
-        <v>68.6916766193267</v>
+        <v>478.1510000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>477.8779979021814</v>
+        <v>70.10600000000002</v>
       </c>
       <c r="X22" t="n">
-        <v>69.05057678488305</v>
+        <v>476.615</v>
       </c>
       <c r="Y22" t="n">
-        <v>478.6800242638351</v>
+        <v>69.78450000000001</v>
       </c>
       <c r="Z22" t="n">
-        <v>70.05129627038716</v>
+        <v>478.0425</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>68.804</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>478.284</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>68.8305</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>478.1195000000001</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>68.691</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>477.8774999999999</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>69.0505</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>478.679</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>70.051</v>
       </c>
       <c r="AJ22" t="n">
-        <v>499.4950000000001</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>499.5833333333333</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>499.719375</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>499.4955</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>499.5835000000001</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>499.7185000000001</v>
+      </c>
+      <c r="AV22" t="n">
         <v>499.4924999999999</v>
       </c>
-      <c r="AN22" t="n">
-        <v>499.6362499999999</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>499.7567857142857</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>499.6334375</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>499.611388888889</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>499.5615000000001</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>90.40453240214721</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>86.06549279293085</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>84.344253989137</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>82.79035594938365</v>
-      </c>
       <c r="AW22" t="n">
-        <v>82.13393599614514</v>
+        <v>499.6365</v>
       </c>
       <c r="AX22" t="n">
-        <v>81.5824733905052</v>
+        <v>499.756</v>
       </c>
       <c r="AY22" t="n">
-        <v>81.23693732856073</v>
+        <v>499.6329999999999</v>
       </c>
       <c r="AZ22" t="n">
-        <v>80.8701194105258</v>
+        <v>499.6115000000001</v>
       </c>
       <c r="BA22" t="n">
-        <v>81.50871794728201</v>
+        <v>499.561</v>
       </c>
       <c r="BB22" t="n">
+        <v>90.40599999999999</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>86.06449999999998</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>84.34400000000001</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>82.7895</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>82.134</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>81.5825</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>81.236</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>80.87050000000001</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>81.50749999999998</v>
+      </c>
+      <c r="BK22" t="n">
         <v>340.9</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BL22" t="n">
         <v>340.55</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BM22" t="n">
         <v>340.35</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BN22" t="n">
         <v>340.25</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BO22" t="n">
         <v>339.25</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BP22" t="n">
         <v>339.25</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BQ22" t="n">
         <v>339.25</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BR22" t="n">
         <v>338.75</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BS22" t="n">
         <v>338.75</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BT22" t="n">
         <v>659.3</v>
       </c>
-      <c r="BL22" t="n">
+      <c r="BU22" t="n">
         <v>659.75</v>
       </c>
-      <c r="BM22" t="n">
+      <c r="BV22" t="n">
         <v>660.5</v>
       </c>
-      <c r="BN22" t="n">
+      <c r="BW22" t="n">
         <v>660.5</v>
       </c>
-      <c r="BO22" t="n">
+      <c r="BX22" t="n">
         <v>661.55</v>
       </c>
-      <c r="BP22" t="n">
+      <c r="BY22" t="n">
         <v>661.7</v>
       </c>
-      <c r="BQ22" t="n">
+      <c r="BZ22" t="n">
         <v>661.7</v>
       </c>
-      <c r="BR22" t="n">
+      <c r="CA22" t="n">
         <v>661.85</v>
       </c>
-      <c r="BS22" t="n">
+      <c r="CB22" t="n">
         <v>661.85</v>
       </c>
-      <c r="BT22" t="n">
-        <v>0.6980518093018093</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0.7522435897435897</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0.7621949106786835</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0.7365738227712113</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0.8094445106199804</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0.8610957539456117</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0.8771388512907882</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0.8671245235351097</v>
-      </c>
-      <c r="CB22" t="n">
-        <v>0.8429139745066913</v>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="n">
+        <v>478.679</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>70.051</v>
       </c>
     </row>
     <row r="23">
@@ -6002,10 +6732,10 @@
         <v>1.496487114615601</v>
       </c>
       <c r="C23" t="n">
+        <v>2.063313191811591</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.391704747876919</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.063313191811591</v>
       </c>
       <c r="E23" t="n">
         <v>1.496487114615601</v>
@@ -6014,224 +6744,239 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.02955258471196544</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>1.302578414651413</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3464861203265542</v>
+      </c>
       <c r="I23" t="n">
-        <v>20.69583826360386</v>
+        <v>0.3171484792565414</v>
       </c>
       <c r="J23" t="n">
-        <v>18.65172257934421</v>
+        <v>0.3246775728561945</v>
       </c>
       <c r="K23" t="n">
-        <v>16.86174108164483</v>
+        <v>0.3103495482601242</v>
       </c>
       <c r="L23" t="n">
-        <v>16.78601254332134</v>
+        <v>0.2996576994540692</v>
       </c>
       <c r="M23" t="n">
-        <v>14.52059262749568</v>
+        <v>0.2846401236649534</v>
       </c>
       <c r="N23" t="n">
-        <v>15.21207729190872</v>
+        <v>0.2858578962388573</v>
       </c>
       <c r="O23" t="n">
-        <v>12.19163946305338</v>
+        <v>0.2558494623180222</v>
       </c>
       <c r="P23" t="n">
-        <v>13.90803724953997</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>8.862021206939611</v>
-      </c>
+        <v>0.3070654824729016</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>11.74210875504179</v>
+        <v>20.69692766419311</v>
       </c>
       <c r="S23" t="n">
-        <v>9.008850978016286</v>
+        <v>18.65309746396024</v>
       </c>
       <c r="T23" t="n">
-        <v>10.80382726595534</v>
+        <v>16.86122674565588</v>
       </c>
       <c r="U23" t="n">
-        <v>9.810430198292188</v>
+        <v>16.78629681583981</v>
       </c>
       <c r="V23" t="n">
-        <v>10.04118653445439</v>
+        <v>14.5206023870985</v>
       </c>
       <c r="W23" t="n">
-        <v>9.013447785385912</v>
+        <v>15.21256212200264</v>
       </c>
       <c r="X23" t="n">
-        <v>8.309481776298345</v>
+        <v>12.19122656926521</v>
       </c>
       <c r="Y23" t="n">
-        <v>9.35956196060404</v>
+        <v>13.90874373796645</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.615617637300779</v>
+        <v>8.862398318027033</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>11.74285691052448</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>9.008332633851019</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>10.80343779349401</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>9.810939906150951</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>10.04136544499801</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>9.014012410510764</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>8.30951482211491</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>9.358482726776202</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>7.614912585460883</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3.121641353013201</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.327467564362159</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.496387109799621</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>3.121825503400886</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.326674326383607</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>2.495894049286384</v>
+      </c>
+      <c r="AV23" t="n">
         <v>1.99283684334933</v>
       </c>
-      <c r="AN23" t="n">
-        <v>1.803197847733342</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1.619612402412826</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.702632292323224</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.691397869924756</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.902919571273794</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>15.93046018594289</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>14.17965267677191</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>14.43573207278772</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>13.71292424471986</v>
-      </c>
       <c r="AW23" t="n">
-        <v>12.85962868271617</v>
+        <v>1.80391467589094</v>
       </c>
       <c r="AX23" t="n">
-        <v>11.3653262841117</v>
+        <v>1.619962312752009</v>
       </c>
       <c r="AY23" t="n">
-        <v>10.16602696406391</v>
+        <v>1.703096560602728</v>
       </c>
       <c r="AZ23" t="n">
-        <v>8.791591827299747</v>
+        <v>1.692050375634315</v>
       </c>
       <c r="BA23" t="n">
-        <v>8.453935152866547</v>
+        <v>1.903569776692422</v>
       </c>
       <c r="BB23" t="n">
+        <v>15.93056459831392</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>14.17919657548748</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>14.43622760171164</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>13.71345842018363</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>12.859636321288</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>11.36647928409626</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>10.16626278173884</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>8.791715882459734</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>8.454037886060565</v>
+      </c>
+      <c r="BK23" t="n">
         <v>23.62848414854188</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BL23" t="n">
         <v>23.50694186382979</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BM23" t="n">
         <v>23.4840931606683</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BN23" t="n">
         <v>23.33255011216824</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BO23" t="n">
         <v>21.97336904911081</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BP23" t="n">
         <v>21.97336904911081</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BQ23" t="n">
         <v>21.97336904911081</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BR23" t="n">
         <v>21.61109607780713</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BS23" t="n">
         <v>21.61109607780713</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BT23" t="n">
         <v>21.47973341008731</v>
       </c>
-      <c r="BL23" t="n">
+      <c r="BU23" t="n">
         <v>20.43957719204274</v>
       </c>
-      <c r="BM23" t="n">
+      <c r="BV23" t="n">
         <v>19.08016330063628</v>
       </c>
-      <c r="BN23" t="n">
+      <c r="BW23" t="n">
         <v>19.08016330063628</v>
       </c>
-      <c r="BO23" t="n">
+      <c r="BX23" t="n">
         <v>16.76611557812206</v>
       </c>
-      <c r="BP23" t="n">
+      <c r="BY23" t="n">
         <v>16.5659765467469</v>
       </c>
-      <c r="BQ23" t="n">
+      <c r="BZ23" t="n">
         <v>16.5659765467469</v>
       </c>
-      <c r="BR23" t="n">
+      <c r="CA23" t="n">
         <v>16.39086716180048</v>
       </c>
-      <c r="BS23" t="n">
+      <c r="CB23" t="n">
         <v>16.39086716180048</v>
       </c>
-      <c r="BT23" t="n">
-        <v>0.2770344708263239</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>0.284250781142971</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>0.2131996101299868</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>0.2274585772437365</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>0.09190139780061655</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>0.09080776447407503</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>0.09819688101742655</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>0.1053516688229722</v>
-      </c>
-      <c r="CB23" t="n">
-        <v>0.108689955460884</v>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="n">
+        <v>9.358482726776202</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>7.614912585460883</v>
       </c>
     </row>
   </sheetData>
